--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ/ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ/ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="82">
   <si>
     <t>Дата</t>
   </si>
@@ -53,51 +53,6 @@
   </si>
   <si>
     <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>2026-05-02</t>
-  </si>
-  <si>
-    <t>2026-05-03</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>2026-05-05</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-05-09</t>
-  </si>
-  <si>
-    <t>2026-05-10</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>2026-05-12</t>
-  </si>
-  <si>
-    <t>2026-05-13</t>
-  </si>
-  <si>
-    <t>2026-05-14</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
   </si>
   <si>
     <t>В8980ВР</t>
@@ -311,8 +266,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -398,11 +354,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -410,9 +367,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -766,20 +723,20 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
+      <c r="A2" s="2">
+        <v>46143</v>
       </c>
       <c r="B2">
         <v>1148</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F2">
         <v>29.289</v>
@@ -797,7 +754,7 @@
         <v>24.31</v>
       </c>
       <c r="K2" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -807,20 +764,20 @@
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>13</v>
+      <c r="A3" s="2">
+        <v>46143</v>
       </c>
       <c r="B3">
         <v>1148</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F3">
         <v>26.795</v>
@@ -838,7 +795,7 @@
         <v>22.24</v>
       </c>
       <c r="K3" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -848,20 +805,20 @@
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>13</v>
+      <c r="A4" s="2">
+        <v>46143</v>
       </c>
       <c r="B4">
         <v>1158</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F4">
         <v>23.506</v>
@@ -879,7 +836,7 @@
         <v>19.51</v>
       </c>
       <c r="K4" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -889,20 +846,20 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" t="s">
-        <v>14</v>
+      <c r="A5" s="2">
+        <v>46144</v>
       </c>
       <c r="B5">
         <v>1148</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F5">
         <v>21.313</v>
@@ -920,7 +877,7 @@
         <v>17.69</v>
       </c>
       <c r="K5" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -930,20 +887,20 @@
       </c>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" t="s">
-        <v>14</v>
+      <c r="A6" s="2">
+        <v>46144</v>
       </c>
       <c r="B6">
         <v>1148</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F6">
         <v>20.88</v>
@@ -961,7 +918,7 @@
         <v>17.33</v>
       </c>
       <c r="K6" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -971,20 +928,20 @@
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" t="s">
-        <v>15</v>
+      <c r="A7" s="2">
+        <v>46145</v>
       </c>
       <c r="B7">
         <v>1148</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="E7" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F7">
         <v>24.229</v>
@@ -1002,7 +959,7 @@
         <v>20.11</v>
       </c>
       <c r="K7" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -1012,20 +969,20 @@
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" t="s">
-        <v>15</v>
+      <c r="A8" s="2">
+        <v>46145</v>
       </c>
       <c r="B8">
         <v>1148</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F8">
         <v>20.976</v>
@@ -1043,7 +1000,7 @@
         <v>17.41</v>
       </c>
       <c r="K8" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -1053,20 +1010,20 @@
       </c>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" t="s">
-        <v>15</v>
+      <c r="A9" s="2">
+        <v>46145</v>
       </c>
       <c r="B9">
         <v>1158</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F9">
         <v>16.277</v>
@@ -1084,7 +1041,7 @@
         <v>13.51</v>
       </c>
       <c r="K9" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -1094,20 +1051,20 @@
       </c>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" t="s">
-        <v>15</v>
+      <c r="A10" s="2">
+        <v>46145</v>
       </c>
       <c r="B10">
         <v>1158</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="E10" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F10">
         <v>15</v>
@@ -1125,7 +1082,7 @@
         <v>22.8</v>
       </c>
       <c r="K10" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -1135,20 +1092,20 @@
       </c>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11" t="s">
-        <v>15</v>
+      <c r="A11" s="2">
+        <v>46145</v>
       </c>
       <c r="B11">
         <v>1158</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E11" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F11">
         <v>16.829</v>
@@ -1166,7 +1123,7 @@
         <v>25.58</v>
       </c>
       <c r="K11" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -1176,20 +1133,20 @@
       </c>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" t="s">
-        <v>15</v>
+      <c r="A12" s="2">
+        <v>46145</v>
       </c>
       <c r="B12">
         <v>1199</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="E12" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F12">
         <v>13.795</v>
@@ -1207,7 +1164,7 @@
         <v>11.45</v>
       </c>
       <c r="K12" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1217,20 +1174,20 @@
       </c>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" t="s">
-        <v>16</v>
+      <c r="A13" s="2">
+        <v>46146</v>
       </c>
       <c r="B13">
         <v>1146</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="E13" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F13">
         <v>24.373</v>
@@ -1248,7 +1205,7 @@
         <v>20.23</v>
       </c>
       <c r="K13" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -1258,20 +1215,20 @@
       </c>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" t="s">
-        <v>16</v>
+      <c r="A14" s="2">
+        <v>46146</v>
       </c>
       <c r="B14">
         <v>1158</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E14" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F14">
         <v>20.205</v>
@@ -1289,7 +1246,7 @@
         <v>16.77</v>
       </c>
       <c r="K14" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -1299,20 +1256,20 @@
       </c>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" t="s">
-        <v>17</v>
+      <c r="A15" s="2">
+        <v>46147</v>
       </c>
       <c r="B15">
         <v>1148</v>
       </c>
       <c r="C15" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="D15" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F15">
         <v>10</v>
@@ -1330,7 +1287,7 @@
         <v>15.2</v>
       </c>
       <c r="K15" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -1340,20 +1297,20 @@
       </c>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" t="s">
-        <v>17</v>
+      <c r="A16" s="2">
+        <v>46147</v>
       </c>
       <c r="B16">
         <v>1148</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E16" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F16">
         <v>26.952</v>
@@ -1371,7 +1328,7 @@
         <v>22.37</v>
       </c>
       <c r="K16" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -1381,20 +1338,20 @@
       </c>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" t="s">
-        <v>17</v>
+      <c r="A17" s="2">
+        <v>46147</v>
       </c>
       <c r="B17">
         <v>1158</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D17" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="E17" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F17">
         <v>21.072</v>
@@ -1412,7 +1369,7 @@
         <v>17.49</v>
       </c>
       <c r="K17" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -1422,20 +1379,20 @@
       </c>
     </row>
     <row r="18" spans="1:13">
-      <c r="A18" t="s">
-        <v>17</v>
+      <c r="A18" s="2">
+        <v>46147</v>
       </c>
       <c r="B18">
         <v>1158</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D18" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F18">
         <v>23.446</v>
@@ -1453,7 +1410,7 @@
         <v>19.46</v>
       </c>
       <c r="K18" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -1463,20 +1420,20 @@
       </c>
     </row>
     <row r="19" spans="1:13">
-      <c r="A19" t="s">
-        <v>18</v>
+      <c r="A19" s="2">
+        <v>46148</v>
       </c>
       <c r="B19">
         <v>1148</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D19" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="E19" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F19">
         <v>17.663</v>
@@ -1494,7 +1451,7 @@
         <v>14.66</v>
       </c>
       <c r="K19" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -1504,20 +1461,20 @@
       </c>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" t="s">
-        <v>18</v>
+      <c r="A20" s="2">
+        <v>46148</v>
       </c>
       <c r="B20">
         <v>1148</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E20" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="F20">
         <v>13</v>
@@ -1535,7 +1492,7 @@
         <v>23.14</v>
       </c>
       <c r="K20" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -1545,20 +1502,20 @@
       </c>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" t="s">
-        <v>18</v>
+      <c r="A21" s="2">
+        <v>46148</v>
       </c>
       <c r="B21">
         <v>1148</v>
       </c>
       <c r="C21" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="E21" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="F21">
         <v>13</v>
@@ -1576,7 +1533,7 @@
         <v>23.14</v>
       </c>
       <c r="K21" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -1586,20 +1543,20 @@
       </c>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" t="s">
-        <v>19</v>
+      <c r="A22" s="2">
+        <v>46149</v>
       </c>
       <c r="B22">
         <v>1146</v>
       </c>
       <c r="C22" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="E22" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F22">
         <v>37.627</v>
@@ -1617,7 +1574,7 @@
         <v>31.23</v>
       </c>
       <c r="K22" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -1627,20 +1584,20 @@
       </c>
     </row>
     <row r="23" spans="1:13">
-      <c r="A23" t="s">
-        <v>19</v>
+      <c r="A23" s="2">
+        <v>46149</v>
       </c>
       <c r="B23">
         <v>1146</v>
       </c>
       <c r="C23" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D23" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="E23" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F23">
         <v>10</v>
@@ -1658,7 +1615,7 @@
         <v>15.3</v>
       </c>
       <c r="K23" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -1668,20 +1625,20 @@
       </c>
     </row>
     <row r="24" spans="1:13">
-      <c r="A24" t="s">
-        <v>19</v>
+      <c r="A24" s="2">
+        <v>46149</v>
       </c>
       <c r="B24">
         <v>1148</v>
       </c>
       <c r="C24" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="D24" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="E24" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F24">
         <v>26.446</v>
@@ -1699,7 +1656,7 @@
         <v>21.95</v>
       </c>
       <c r="K24" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -1709,20 +1666,20 @@
       </c>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" t="s">
-        <v>19</v>
+      <c r="A25" s="2">
+        <v>46149</v>
       </c>
       <c r="B25">
         <v>1158</v>
       </c>
       <c r="C25" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D25" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E25" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F25">
         <v>12.361</v>
@@ -1740,7 +1697,7 @@
         <v>10.26</v>
       </c>
       <c r="K25" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -1750,20 +1707,20 @@
       </c>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" t="s">
-        <v>19</v>
+      <c r="A26" s="2">
+        <v>46149</v>
       </c>
       <c r="B26">
         <v>1158</v>
       </c>
       <c r="C26" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="E26" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F26">
         <v>20.265</v>
@@ -1781,7 +1738,7 @@
         <v>16.82</v>
       </c>
       <c r="K26" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -1791,20 +1748,20 @@
       </c>
     </row>
     <row r="27" spans="1:13">
-      <c r="A27" t="s">
-        <v>20</v>
+      <c r="A27" s="2">
+        <v>46150</v>
       </c>
       <c r="B27">
         <v>1146</v>
       </c>
       <c r="C27" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="D27" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="E27" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F27">
         <v>19.566</v>
@@ -1822,7 +1779,7 @@
         <v>16.24</v>
       </c>
       <c r="K27" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -1832,20 +1789,20 @@
       </c>
     </row>
     <row r="28" spans="1:13">
-      <c r="A28" t="s">
-        <v>20</v>
+      <c r="A28" s="2">
+        <v>46150</v>
       </c>
       <c r="B28">
         <v>1158</v>
       </c>
       <c r="C28" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D28" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E28" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F28">
         <v>24.639</v>
@@ -1863,7 +1820,7 @@
         <v>20.45</v>
       </c>
       <c r="K28" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -1873,20 +1830,20 @@
       </c>
     </row>
     <row r="29" spans="1:13">
-      <c r="A29" t="s">
-        <v>21</v>
+      <c r="A29" s="2">
+        <v>46151</v>
       </c>
       <c r="B29">
         <v>1148</v>
       </c>
       <c r="C29" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D29" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E29" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="F29">
         <v>16</v>
@@ -1904,7 +1861,7 @@
         <v>28.64</v>
       </c>
       <c r="K29" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -1914,20 +1871,20 @@
       </c>
     </row>
     <row r="30" spans="1:13">
-      <c r="A30" t="s">
-        <v>21</v>
+      <c r="A30" s="2">
+        <v>46151</v>
       </c>
       <c r="B30">
         <v>1148</v>
       </c>
       <c r="C30" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D30" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="E30" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="F30">
         <v>17.659</v>
@@ -1945,7 +1902,7 @@
         <v>31.61</v>
       </c>
       <c r="K30" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -1955,20 +1912,20 @@
       </c>
     </row>
     <row r="31" spans="1:13">
-      <c r="A31" t="s">
-        <v>22</v>
+      <c r="A31" s="2">
+        <v>46152</v>
       </c>
       <c r="B31">
         <v>1158</v>
       </c>
       <c r="C31" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D31" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="E31" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F31">
         <v>12</v>
@@ -1986,7 +1943,7 @@
         <v>18.48</v>
       </c>
       <c r="K31" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -1996,20 +1953,20 @@
       </c>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" t="s">
-        <v>22</v>
+      <c r="A32" s="2">
+        <v>46152</v>
       </c>
       <c r="B32">
         <v>1158</v>
       </c>
       <c r="C32" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="E32" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F32">
         <v>26.482</v>
@@ -2027,7 +1984,7 @@
         <v>21.98</v>
       </c>
       <c r="K32" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -2037,20 +1994,20 @@
       </c>
     </row>
     <row r="33" spans="1:13">
-      <c r="A33" t="s">
-        <v>22</v>
+      <c r="A33" s="2">
+        <v>46152</v>
       </c>
       <c r="B33">
         <v>1158</v>
       </c>
       <c r="C33" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="D33" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="E33" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F33">
         <v>25.12</v>
@@ -2068,7 +2025,7 @@
         <v>20.85</v>
       </c>
       <c r="K33" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -2078,20 +2035,20 @@
       </c>
     </row>
     <row r="34" spans="1:13">
-      <c r="A34" t="s">
-        <v>22</v>
+      <c r="A34" s="2">
+        <v>46152</v>
       </c>
       <c r="B34">
         <v>1911</v>
       </c>
       <c r="C34" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D34" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E34" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F34">
         <v>25.325</v>
@@ -2109,7 +2066,7 @@
         <v>21.02</v>
       </c>
       <c r="K34" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -2119,20 +2076,20 @@
       </c>
     </row>
     <row r="35" spans="1:13">
-      <c r="A35" t="s">
-        <v>23</v>
+      <c r="A35" s="2">
+        <v>46153</v>
       </c>
       <c r="B35">
         <v>1158</v>
       </c>
       <c r="C35" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D35" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="E35" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F35">
         <v>22.386</v>
@@ -2150,7 +2107,7 @@
         <v>18.58</v>
       </c>
       <c r="K35" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -2160,20 +2117,20 @@
       </c>
     </row>
     <row r="36" spans="1:13">
-      <c r="A36" t="s">
-        <v>24</v>
+      <c r="A36" s="2">
+        <v>46154</v>
       </c>
       <c r="B36">
         <v>1148</v>
       </c>
       <c r="C36" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D36" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E36" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F36">
         <v>24.537</v>
@@ -2191,7 +2148,7 @@
         <v>20.12</v>
       </c>
       <c r="K36" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -2201,20 +2158,20 @@
       </c>
     </row>
     <row r="37" spans="1:13">
-      <c r="A37" t="s">
-        <v>24</v>
+      <c r="A37" s="2">
+        <v>46154</v>
       </c>
       <c r="B37">
         <v>1158</v>
       </c>
       <c r="C37" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D37" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="E37" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F37">
         <v>19.39</v>
@@ -2232,7 +2189,7 @@
         <v>15.9</v>
       </c>
       <c r="K37" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -2242,20 +2199,20 @@
       </c>
     </row>
     <row r="38" spans="1:13">
-      <c r="A38" t="s">
-        <v>25</v>
+      <c r="A38" s="2">
+        <v>46155</v>
       </c>
       <c r="B38">
         <v>1148</v>
       </c>
       <c r="C38" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E38" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F38">
         <v>25.765</v>
@@ -2273,7 +2230,7 @@
         <v>20.87</v>
       </c>
       <c r="K38" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -2283,20 +2240,20 @@
       </c>
     </row>
     <row r="39" spans="1:13">
-      <c r="A39" t="s">
-        <v>25</v>
+      <c r="A39" s="2">
+        <v>46155</v>
       </c>
       <c r="B39">
         <v>1158</v>
       </c>
       <c r="C39" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="E39" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F39">
         <v>14</v>
@@ -2314,7 +2271,7 @@
         <v>21.56</v>
       </c>
       <c r="K39" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -2324,20 +2281,20 @@
       </c>
     </row>
     <row r="40" spans="1:13">
-      <c r="A40" t="s">
-        <v>25</v>
+      <c r="A40" s="2">
+        <v>46155</v>
       </c>
       <c r="B40">
         <v>1158</v>
       </c>
       <c r="C40" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D40" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E40" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F40">
         <v>15.779</v>
@@ -2355,7 +2312,7 @@
         <v>24.3</v>
       </c>
       <c r="K40" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -2365,20 +2322,20 @@
       </c>
     </row>
     <row r="41" spans="1:13">
-      <c r="A41" t="s">
-        <v>26</v>
+      <c r="A41" s="2">
+        <v>46156</v>
       </c>
       <c r="B41">
         <v>1146</v>
       </c>
       <c r="C41" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D41" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E41" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F41">
         <v>22.259</v>
@@ -2396,7 +2353,7 @@
         <v>18.03</v>
       </c>
       <c r="K41" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -2406,20 +2363,20 @@
       </c>
     </row>
     <row r="42" spans="1:13">
-      <c r="A42" t="s">
-        <v>26</v>
+      <c r="A42" s="2">
+        <v>46156</v>
       </c>
       <c r="B42">
         <v>1147</v>
       </c>
       <c r="C42" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="D42" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="E42" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F42">
         <v>25.593</v>
@@ -2437,7 +2394,7 @@
         <v>20.73</v>
       </c>
       <c r="K42" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -2447,20 +2404,20 @@
       </c>
     </row>
     <row r="43" spans="1:13">
-      <c r="A43" t="s">
-        <v>26</v>
+      <c r="A43" s="2">
+        <v>46156</v>
       </c>
       <c r="B43">
         <v>1148</v>
       </c>
       <c r="C43" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D43" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="E43" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F43">
         <v>21.716</v>
@@ -2478,7 +2435,7 @@
         <v>17.59</v>
       </c>
       <c r="K43" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -2488,20 +2445,20 @@
       </c>
     </row>
     <row r="44" spans="1:13">
-      <c r="A44" t="s">
-        <v>26</v>
+      <c r="A44" s="2">
+        <v>46156</v>
       </c>
       <c r="B44">
         <v>1911</v>
       </c>
       <c r="C44" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D44" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="E44" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F44">
         <v>21.173</v>
@@ -2519,7 +2476,7 @@
         <v>17.15</v>
       </c>
       <c r="K44" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -2529,20 +2486,20 @@
       </c>
     </row>
     <row r="45" spans="1:13">
-      <c r="A45" t="s">
-        <v>27</v>
+      <c r="A45" s="2">
+        <v>46157</v>
       </c>
       <c r="B45">
         <v>1158</v>
       </c>
       <c r="C45" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E45" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F45">
         <v>19.25</v>
@@ -2560,7 +2517,7 @@
         <v>15.4</v>
       </c>
       <c r="K45" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -2570,126 +2527,126 @@
       </c>
     </row>
     <row r="48" spans="1:13">
-      <c r="A48" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
+      <c r="A48" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>95</v>
+      <c r="A49" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="4" t="s">
+      <c r="A50" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B50" s="6">
+        <v>750.671</v>
+      </c>
+      <c r="C50" s="6">
+        <v>33</v>
+      </c>
+      <c r="D50" s="6">
+        <v>0.8156</v>
+      </c>
+      <c r="E50" s="6">
+        <v>612.22</v>
+      </c>
+      <c r="F50" s="6">
+        <v>619.71</v>
+      </c>
+      <c r="G50" s="6">
+        <v>7.49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B51" s="6">
+        <v>93.608</v>
+      </c>
+      <c r="C51" s="6">
+        <v>7</v>
+      </c>
+      <c r="D51" s="6">
+        <v>1.5001</v>
+      </c>
+      <c r="E51" s="6">
+        <v>140.42</v>
+      </c>
+      <c r="F51" s="6">
+        <v>143.22</v>
+      </c>
+      <c r="G51" s="6">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B52" s="6">
+        <v>59.659</v>
+      </c>
+      <c r="C52" s="6">
+        <v>4</v>
+      </c>
+      <c r="D52" s="6">
+        <v>1.7456</v>
+      </c>
+      <c r="E52" s="6">
+        <v>104.14</v>
+      </c>
+      <c r="F52" s="6">
+        <v>106.53</v>
+      </c>
+      <c r="G52" s="6">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B53" s="8">
+        <v>903.938</v>
+      </c>
+      <c r="C53" s="8">
         <v>44</v>
       </c>
-      <c r="B50" s="5">
-        <v>750.671</v>
-      </c>
-      <c r="C50" s="5">
-        <v>33</v>
-      </c>
-      <c r="D50" s="5">
-        <v>0.8156</v>
-      </c>
-      <c r="E50" s="5">
-        <v>612.22</v>
-      </c>
-      <c r="F50" s="5">
-        <v>619.71</v>
-      </c>
-      <c r="G50" s="5">
-        <v>7.49</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="5">
-        <v>93.608</v>
-      </c>
-      <c r="C51" s="5">
-        <v>7</v>
-      </c>
-      <c r="D51" s="5">
-        <v>1.5001</v>
-      </c>
-      <c r="E51" s="5">
-        <v>140.42</v>
-      </c>
-      <c r="F51" s="5">
-        <v>143.22</v>
-      </c>
-      <c r="G51" s="5">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B52" s="5">
-        <v>59.659</v>
-      </c>
-      <c r="C52" s="5">
-        <v>4</v>
-      </c>
-      <c r="D52" s="5">
-        <v>1.7456</v>
-      </c>
-      <c r="E52" s="5">
-        <v>104.14</v>
-      </c>
-      <c r="F52" s="5">
-        <v>106.53</v>
-      </c>
-      <c r="G52" s="5">
-        <v>2.39</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B53" s="7">
-        <v>903.938</v>
-      </c>
-      <c r="C53" s="7">
-        <v>44</v>
-      </c>
-      <c r="D53" s="7"/>
-      <c r="E53" s="7">
+      <c r="D53" s="8"/>
+      <c r="E53" s="8">
         <v>856.78</v>
       </c>
-      <c r="F53" s="7">
+      <c r="F53" s="8">
         <v>869.46</v>
       </c>
-      <c r="G53" s="7">
+      <c r="G53" s="8">
         <v>12.68</v>
       </c>
     </row>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ/ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ/ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ.xlsx
@@ -386,7 +386,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -396,12 +396,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,17 +446,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ/ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ/ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="72">
   <si>
     <t>Дата</t>
   </si>
@@ -46,9 +46,15 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
+    <t>Час</t>
+  </si>
+  <si>
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>Варна Порт</t>
   </si>
   <si>
@@ -58,7 +64,7 @@
     <t>Варна Сливница</t>
   </si>
   <si>
-    <t>Варна</t>
+    <t>Варна Евkсиноград</t>
   </si>
   <si>
     <t>В8977ВР</t>
@@ -101,6 +107,111 @@
   </si>
   <si>
     <t>95 EKONOMY UNLEADED</t>
+  </si>
+  <si>
+    <t>09:33</t>
+  </si>
+  <si>
+    <t>09:35</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>13:04</t>
+  </si>
+  <si>
+    <t>13:05</t>
+  </si>
+  <si>
+    <t>10:01</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>06:16</t>
+  </si>
+  <si>
+    <t>08:46</t>
+  </si>
+  <si>
+    <t>08:50</t>
+  </si>
+  <si>
+    <t>22:31</t>
+  </si>
+  <si>
+    <t>22:36</t>
+  </si>
+  <si>
+    <t>16:09</t>
+  </si>
+  <si>
+    <t>16:47</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>08:44</t>
+  </si>
+  <si>
+    <t>10:04</t>
+  </si>
+  <si>
+    <t>12:04</t>
+  </si>
+  <si>
+    <t>08:33</t>
+  </si>
+  <si>
+    <t>10:06</t>
+  </si>
+  <si>
+    <t>13:53</t>
+  </si>
+  <si>
+    <t>09:45</t>
+  </si>
+  <si>
+    <t>20:16</t>
+  </si>
+  <si>
+    <t>07:10</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>09:58</t>
+  </si>
+  <si>
+    <t>11:34</t>
+  </si>
+  <si>
+    <t>07:03</t>
+  </si>
+  <si>
+    <t>10:56</t>
+  </si>
+  <si>
+    <t>06:22</t>
+  </si>
+  <si>
+    <t>12:16</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>08:54</t>
+  </si>
+  <si>
+    <t>17:17</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ</t>
@@ -520,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -533,10 +644,12 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -570,22 +683,28 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46174</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F2">
         <v>25.78</v>
@@ -602,25 +721,31 @@
       <c r="J2">
         <v>19.85</v>
       </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="K2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>213389</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46174</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F3">
         <v>10</v>
@@ -637,25 +762,31 @@
       <c r="J3">
         <v>15.7</v>
       </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>213393</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46174</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F4">
         <v>37.42</v>
@@ -672,25 +803,31 @@
       <c r="J4">
         <v>28.81</v>
       </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="K4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>105880</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
         <v>46174</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F5">
         <v>10</v>
@@ -707,25 +844,31 @@
       <c r="J5">
         <v>15.7</v>
       </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="K5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>137427</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="3">
         <v>46174</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F6">
         <v>22.82</v>
@@ -742,25 +885,31 @@
       <c r="J6">
         <v>17.57</v>
       </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="K6" t="s">
+        <v>35</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>137428</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="3">
         <v>46175</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F7">
         <v>17.44</v>
@@ -777,25 +926,31 @@
       <c r="J7">
         <v>13.08</v>
       </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="K7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>213845</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="3">
         <v>46175</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F8">
         <v>23.59</v>
@@ -812,25 +967,31 @@
       <c r="J8">
         <v>17.69</v>
       </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="K8" t="s">
+        <v>37</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>213989</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="3">
         <v>46176</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F9">
         <v>27.64</v>
@@ -847,25 +1008,31 @@
       <c r="J9">
         <v>20.73</v>
       </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="K9" t="s">
+        <v>38</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>106700</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="3">
         <v>46176</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F10">
         <v>21.67</v>
@@ -882,25 +1049,31 @@
       <c r="J10">
         <v>16.25</v>
       </c>
-      <c r="K10">
+      <c r="K10" t="s">
+        <v>39</v>
+      </c>
+      <c r="L10">
         <v>195711</v>
       </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="M10">
+        <v>106784</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="3">
         <v>46176</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F11">
         <v>10</v>
@@ -917,25 +1090,31 @@
       <c r="J11">
         <v>15.7</v>
       </c>
-      <c r="K11">
+      <c r="K11" t="s">
+        <v>40</v>
+      </c>
+      <c r="L11">
         <v>195711</v>
       </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="M11">
+        <v>106790</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="3">
         <v>46176</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E12" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F12">
         <v>10</v>
@@ -952,25 +1131,31 @@
       <c r="J12">
         <v>15.7</v>
       </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="K12" t="s">
+        <v>41</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>214573</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="3">
         <v>46176</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F13">
         <v>29.22</v>
@@ -987,25 +1172,31 @@
       <c r="J13">
         <v>21.62</v>
       </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="K13" t="s">
+        <v>42</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>214574</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="3">
         <v>46177</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E14" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F14">
         <v>22.72</v>
@@ -1022,25 +1213,31 @@
       <c r="J14">
         <v>16.81</v>
       </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="K14" t="s">
+        <v>43</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>138573</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="3">
         <v>46177</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F15">
         <v>14.1</v>
@@ -1057,25 +1254,31 @@
       <c r="J15">
         <v>10.43</v>
       </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="K15" t="s">
+        <v>44</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>214917</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="3">
         <v>46178</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E16" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F16">
         <v>21.32</v>
@@ -1092,25 +1295,31 @@
       <c r="J16">
         <v>15.78</v>
       </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="K16" t="s">
+        <v>45</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>108315</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="3">
         <v>46179</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E17" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F17">
         <v>25.53</v>
@@ -1127,25 +1336,31 @@
       <c r="J17">
         <v>18.64</v>
       </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="K17" t="s">
+        <v>46</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>215515</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="3">
         <v>46180</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D18" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E18" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F18">
         <v>25.88</v>
@@ -1162,25 +1377,31 @@
       <c r="J18">
         <v>18.63</v>
       </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+      <c r="K18" t="s">
+        <v>47</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>139466</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="3">
         <v>46180</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C19" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D19" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E19" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F19">
         <v>25.11</v>
@@ -1197,25 +1418,31 @@
       <c r="J19">
         <v>18.08</v>
       </c>
-      <c r="K19">
+      <c r="K19" t="s">
+        <v>48</v>
+      </c>
+      <c r="L19">
         <v>208992</v>
       </c>
-    </row>
-    <row r="20" spans="1:11">
+      <c r="M19">
+        <v>215950</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="3">
         <v>46181</v>
       </c>
       <c r="B20" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E20" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F20">
         <v>19.29</v>
@@ -1232,25 +1459,31 @@
       <c r="J20">
         <v>13.89</v>
       </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="K20" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>192898</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="3">
         <v>46181</v>
       </c>
       <c r="B21" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C21" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D21" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E21" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F21">
         <v>28</v>
@@ -1267,25 +1500,31 @@
       <c r="J21">
         <v>20.16</v>
       </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+      <c r="K21" t="s">
+        <v>50</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>109397</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="3">
         <v>46181</v>
       </c>
       <c r="B22" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E22" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F22">
         <v>18.67</v>
@@ -1302,25 +1541,31 @@
       <c r="J22">
         <v>13.44</v>
       </c>
-      <c r="K22">
+      <c r="K22" t="s">
+        <v>51</v>
+      </c>
+      <c r="L22">
         <v>153310</v>
       </c>
-    </row>
-    <row r="23" spans="1:11">
+      <c r="M22">
+        <v>109605</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" s="3">
         <v>46182</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D23" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E23" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F23">
         <v>19.93</v>
@@ -1337,25 +1582,31 @@
       <c r="J23">
         <v>14.35</v>
       </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
+      <c r="K23" t="s">
+        <v>52</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>216664</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" s="3">
         <v>46182</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D24" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E24" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F24">
         <v>13.74</v>
@@ -1372,25 +1623,31 @@
       <c r="J24">
         <v>9.890000000000001</v>
       </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
+      <c r="K24" t="s">
+        <v>53</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>110365</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" s="3">
         <v>46183</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D25" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E25" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F25">
         <v>27.99</v>
@@ -1407,25 +1664,31 @@
       <c r="J25">
         <v>20.15</v>
       </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
+      <c r="K25" t="s">
+        <v>54</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>110429</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" s="3">
         <v>46183</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C26" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D26" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E26" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F26">
         <v>26.25</v>
@@ -1442,25 +1705,31 @@
       <c r="J26">
         <v>18.64</v>
       </c>
-      <c r="K26">
+      <c r="K26" t="s">
+        <v>55</v>
+      </c>
+      <c r="L26">
         <v>195887</v>
       </c>
-    </row>
-    <row r="27" spans="1:11">
+      <c r="M26">
+        <v>110777</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" s="3">
         <v>46183</v>
       </c>
       <c r="B27" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C27" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D27" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E27" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F27">
         <v>20.76</v>
@@ -1477,25 +1746,31 @@
       <c r="J27">
         <v>14.74</v>
       </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
+      <c r="K27" t="s">
+        <v>56</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>111036</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" s="3">
         <v>46184</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C28" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D28" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E28" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F28">
         <v>21.51</v>
@@ -1512,25 +1787,31 @@
       <c r="J28">
         <v>14.84</v>
       </c>
-      <c r="K28">
+      <c r="K28" t="s">
+        <v>57</v>
+      </c>
+      <c r="L28">
         <v>187968</v>
       </c>
-    </row>
-    <row r="29" spans="1:11">
+      <c r="M28">
+        <v>217676</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" s="3">
         <v>46184</v>
       </c>
       <c r="B29" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C29" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D29" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E29" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F29">
         <v>17.32</v>
@@ -1547,25 +1828,31 @@
       <c r="J29">
         <v>11.95</v>
       </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
+      <c r="K29" t="s">
+        <v>58</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>111255</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" s="3">
         <v>46185</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C30" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D30" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E30" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F30">
         <v>23.41</v>
@@ -1582,25 +1869,31 @@
       <c r="J30">
         <v>15.92</v>
       </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
+      <c r="K30" t="s">
+        <v>59</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>218009</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="3">
         <v>46185</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D31" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E31" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F31">
         <v>23.18</v>
@@ -1617,25 +1910,31 @@
       <c r="J31">
         <v>15.76</v>
       </c>
-      <c r="K31">
+      <c r="K31" t="s">
+        <v>60</v>
+      </c>
+      <c r="L31">
         <v>209284</v>
       </c>
-    </row>
-    <row r="32" spans="1:11">
+      <c r="M31">
+        <v>218124</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" s="3">
         <v>46186</v>
       </c>
       <c r="B32" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C32" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D32" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E32" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F32">
         <v>21.26</v>
@@ -1652,25 +1951,31 @@
       <c r="J32">
         <v>14.46</v>
       </c>
-      <c r="K32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
+      <c r="K32" t="s">
+        <v>38</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>112111</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33" s="3">
         <v>46186</v>
       </c>
       <c r="B33" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C33" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D33" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E33" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F33">
         <v>21.22</v>
@@ -1687,25 +1992,31 @@
       <c r="J33">
         <v>14.43</v>
       </c>
-      <c r="K33">
+      <c r="K33" t="s">
+        <v>61</v>
+      </c>
+      <c r="L33">
         <v>209417</v>
       </c>
-    </row>
-    <row r="34" spans="1:11">
+      <c r="M33">
+        <v>112113</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" s="3">
         <v>46186</v>
       </c>
       <c r="B34" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D34" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E34" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F34">
         <v>21.53</v>
@@ -1722,25 +2033,31 @@
       <c r="J34">
         <v>14.64</v>
       </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
+      <c r="K34" t="s">
+        <v>46</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>218502</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35" s="3">
         <v>46186</v>
       </c>
       <c r="B35" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D35" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E35" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F35">
         <v>25.79</v>
@@ -1757,25 +2074,31 @@
       <c r="J35">
         <v>17.54</v>
       </c>
-      <c r="K35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
+      <c r="K35" t="s">
+        <v>62</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>116209</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" s="3">
         <v>46188</v>
       </c>
       <c r="B36" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C36" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D36" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E36" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F36">
         <v>31.56</v>
@@ -1792,25 +2115,31 @@
       <c r="J36">
         <v>21.46</v>
       </c>
-      <c r="K36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11">
+      <c r="K36" t="s">
+        <v>63</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>47768</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
       <c r="A37" s="3">
         <v>46188</v>
       </c>
       <c r="B37" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D37" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E37" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F37">
         <v>23.65</v>
@@ -1827,25 +2156,31 @@
       <c r="J37">
         <v>16.08</v>
       </c>
-      <c r="K37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11">
+      <c r="K37" t="s">
+        <v>64</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>219199</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38" s="3">
         <v>46188</v>
       </c>
       <c r="B38" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C38" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D38" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E38" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F38">
         <v>28.57</v>
@@ -1862,13 +2197,19 @@
       <c r="J38">
         <v>19.43</v>
       </c>
-      <c r="K38">
+      <c r="K38" t="s">
+        <v>65</v>
+      </c>
+      <c r="L38">
         <v>178303</v>
       </c>
-    </row>
-    <row r="41" spans="1:11">
+      <c r="M38">
+        <v>113533</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
       <c r="A41" s="4" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -1876,18 +2217,18 @@
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:13">
       <c r="A42" s="5" t="s">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>7</v>
@@ -1896,9 +2237,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:13">
       <c r="A43" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B43" s="7">
         <v>773.87</v>
@@ -1916,9 +2257,9 @@
         <v>555.74</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:13">
       <c r="A44" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B44" s="7">
         <v>40</v>
@@ -1936,9 +2277,9 @@
         <v>62.8</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:13">
       <c r="A45" s="9" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="B45" s="10">
         <v>813.87</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ/ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ/ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="105">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,27 +52,33 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Варна Чайка</t>
-  </si>
-  <si>
-    <t>Варна Порт</t>
-  </si>
-  <si>
-    <t>Варна Сливница</t>
-  </si>
-  <si>
-    <t>Варна</t>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>1911 O5 Варна</t>
+  </si>
+  <si>
+    <t>В8971ВР</t>
+  </si>
+  <si>
+    <t>В7237ВР</t>
   </si>
   <si>
     <t>В8977ВР</t>
   </si>
   <si>
-    <t>В7237ВР</t>
-  </si>
-  <si>
-    <t>В8971ВР</t>
-  </si>
-  <si>
     <t>В8991ВР</t>
   </si>
   <si>
@@ -79,15 +88,15 @@
     <t>В8982ВР</t>
   </si>
   <si>
+    <t>78970155027722473</t>
+  </si>
+  <si>
+    <t>78970155027722465</t>
+  </si>
+  <si>
     <t>78970155027722481</t>
   </si>
   <si>
-    <t>78970155027722465</t>
-  </si>
-  <si>
-    <t>78970155027722473</t>
-  </si>
-  <si>
     <t>78970155027722515</t>
   </si>
   <si>
@@ -100,73 +109,208 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>2026-06-16 07:03:22</t>
-  </si>
-  <si>
-    <t>2026-06-16 07:03:37</t>
-  </si>
-  <si>
-    <t>2026-06-16 11:44:11</t>
-  </si>
-  <si>
-    <t>2026-06-17 09:07:00</t>
-  </si>
-  <si>
-    <t>2026-06-17 14:00:55</t>
-  </si>
-  <si>
-    <t>2026-06-17 20:37:10</t>
-  </si>
-  <si>
-    <t>2026-06-18 09:56:01</t>
-  </si>
-  <si>
-    <t>2026-06-18 19:36:09</t>
-  </si>
-  <si>
-    <t>2026-06-19 18:34:17</t>
-  </si>
-  <si>
-    <t>2026-06-20 09:06:59</t>
-  </si>
-  <si>
-    <t>2026-06-20 10:20:14</t>
-  </si>
-  <si>
-    <t>2026-06-21 13:29:54</t>
-  </si>
-  <si>
-    <t>2026-06-21 20:30:08</t>
-  </si>
-  <si>
-    <t>2026-06-22 10:33:30</t>
-  </si>
-  <si>
-    <t>2026-06-22 13:25:20</t>
-  </si>
-  <si>
-    <t>2026-06-22 18:19:35</t>
-  </si>
-  <si>
-    <t>2026-06-23 15:13:19</t>
-  </si>
-  <si>
-    <t>2026-06-24 07:17:54</t>
-  </si>
-  <si>
-    <t>2026-06-24 08:38:16</t>
-  </si>
-  <si>
-    <t>2026-06-24 10:35:06</t>
-  </si>
-  <si>
-    <t>2026-06-24 19:08:27</t>
-  </si>
-  <si>
-    <t>2026-06-25 07:18:37</t>
-  </si>
-  <si>
-    <t>2026-06-25 08:45:34</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>11:44:00</t>
+  </si>
+  <si>
+    <t>07:03:00</t>
+  </si>
+  <si>
+    <t>09:07:00</t>
+  </si>
+  <si>
+    <t>14:01:00</t>
+  </si>
+  <si>
+    <t>20:37:00</t>
+  </si>
+  <si>
+    <t>09:56:00</t>
+  </si>
+  <si>
+    <t>19:36:00</t>
+  </si>
+  <si>
+    <t>18:34:00</t>
+  </si>
+  <si>
+    <t>10:19:00</t>
+  </si>
+  <si>
+    <t>13:30:00</t>
+  </si>
+  <si>
+    <t>20:29:00</t>
+  </si>
+  <si>
+    <t>10:33:00</t>
+  </si>
+  <si>
+    <t>13:25:00</t>
+  </si>
+  <si>
+    <t>18:19:00</t>
+  </si>
+  <si>
+    <t>15:13:00</t>
+  </si>
+  <si>
+    <t>08:38:00</t>
+  </si>
+  <si>
+    <t>10:35:00</t>
+  </si>
+  <si>
+    <t>07:18:00</t>
+  </si>
+  <si>
+    <t>19:08:00</t>
+  </si>
+  <si>
+    <t>08:45:00</t>
+  </si>
+  <si>
+    <t>18:41:00</t>
+  </si>
+  <si>
+    <t>06:53:00</t>
+  </si>
+  <si>
+    <t>09:20:00</t>
+  </si>
+  <si>
+    <t>08:25:00</t>
+  </si>
+  <si>
+    <t>14:45:00</t>
+  </si>
+  <si>
+    <t>21:08:00</t>
+  </si>
+  <si>
+    <t>08:35:00</t>
+  </si>
+  <si>
+    <t>08:40:00</t>
+  </si>
+  <si>
+    <t>10:29:00</t>
+  </si>
+  <si>
+    <t>18:16:00</t>
+  </si>
+  <si>
+    <t>14:33:00</t>
+  </si>
+  <si>
+    <t>19:15:00</t>
+  </si>
+  <si>
+    <t>3233437605 3233437605</t>
+  </si>
+  <si>
+    <t>3233411429 3233411429</t>
+  </si>
+  <si>
+    <t>3233411735 3233411735</t>
+  </si>
+  <si>
+    <t>3233485135 3233485135</t>
+  </si>
+  <si>
+    <t>3233490809 3233490809</t>
+  </si>
+  <si>
+    <t>3233495918 3233495918</t>
+  </si>
+  <si>
+    <t>3233529758 3233529758</t>
+  </si>
+  <si>
+    <t>3233542645 3233542645</t>
+  </si>
+  <si>
+    <t>3233595294 3233595294</t>
+  </si>
+  <si>
+    <t>3233637719 3233637719</t>
+  </si>
+  <si>
+    <t>3233607682 3233607682</t>
+  </si>
+  <si>
+    <t>3233674186 3233674186</t>
+  </si>
+  <si>
+    <t>3233692116 3233692116</t>
+  </si>
+  <si>
+    <t>3233710348 3233710348</t>
+  </si>
+  <si>
+    <t>3233722381 3233722381</t>
+  </si>
+  <si>
+    <t>3233731832 3233731832</t>
+  </si>
+  <si>
+    <t>3233767434 3233767434</t>
+  </si>
+  <si>
+    <t>3233782618 3233782618</t>
+  </si>
+  <si>
+    <t>3233805885 3233805885</t>
+  </si>
+  <si>
+    <t>3233808756 3233808756</t>
+  </si>
+  <si>
+    <t>3233808884 3233808884</t>
+  </si>
+  <si>
+    <t>3233854796 3233854796</t>
+  </si>
+  <si>
+    <t>3233855250 3233855250</t>
+  </si>
+  <si>
+    <t>3233950927 3233950927</t>
+  </si>
+  <si>
+    <t>3233872590 3233872590</t>
+  </si>
+  <si>
+    <t>3233945380 3233945380</t>
+  </si>
+  <si>
+    <t>3233945924 3233945924</t>
+  </si>
+  <si>
+    <t>3234013256 3234013256</t>
+  </si>
+  <si>
+    <t>3234020956 3234020956</t>
+  </si>
+  <si>
+    <t>3233998895 3233998895</t>
+  </si>
+  <si>
+    <t>3234049845 3234049845</t>
+  </si>
+  <si>
+    <t>3234051279 3234051279</t>
+  </si>
+  <si>
+    <t>3234057743 3234057743</t>
+  </si>
+  <si>
+    <t>3234100173 3234100173</t>
+  </si>
+  <si>
+    <t>3234098478 3234098478</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ</t>
@@ -586,7 +730,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:N42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -595,14 +739,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -636,883 +783,1627 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46189</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F2">
-        <v>26.4</v>
-      </c>
-      <c r="G2" s="1">
+        <v>21.55</v>
+      </c>
+      <c r="G2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2">
+        <v>0.66</v>
+      </c>
+      <c r="I2" s="1">
+        <v>14.22</v>
+      </c>
+      <c r="J2">
         <v>0.67</v>
       </c>
-      <c r="H2">
-        <v>17.69</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0.68</v>
-      </c>
-      <c r="J2">
-        <v>17.95</v>
-      </c>
-      <c r="K2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="K2" s="1">
+        <v>14.44</v>
+      </c>
+      <c r="L2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2">
+        <v>188337</v>
+      </c>
+      <c r="N2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46189</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F3">
         <v>36.37</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3">
         <v>0.67</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>24.37</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>0.68</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>24.73</v>
       </c>
-      <c r="K3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46189</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F4">
-        <v>21.55</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0.66</v>
+        <v>26.4</v>
+      </c>
+      <c r="G4" t="s">
+        <v>31</v>
       </c>
       <c r="H4">
-        <v>14.22</v>
+        <v>0.67</v>
       </c>
       <c r="I4" s="1">
-        <v>0.67</v>
+        <v>17.69</v>
       </c>
       <c r="J4">
-        <v>14.44</v>
-      </c>
-      <c r="K4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+        <v>0.68</v>
+      </c>
+      <c r="K4" s="1">
+        <v>17.95</v>
+      </c>
+      <c r="L4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46190</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F5">
         <v>30.84</v>
       </c>
-      <c r="G5" s="1">
-        <v>0.66</v>
+      <c r="G5" t="s">
+        <v>31</v>
       </c>
       <c r="H5">
+        <v>0.66</v>
+      </c>
+      <c r="I5" s="1">
         <v>20.35</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>0.67</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>20.66</v>
       </c>
-      <c r="K5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5" t="s">
+        <v>34</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
         <v>46190</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F6">
         <v>25.25</v>
       </c>
-      <c r="G6" s="1">
-        <v>0.66</v>
+      <c r="G6" t="s">
+        <v>31</v>
       </c>
       <c r="H6">
+        <v>0.66</v>
+      </c>
+      <c r="I6" s="1">
         <v>16.66</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>0.67</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>16.92</v>
       </c>
-      <c r="K6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6" t="s">
+        <v>35</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="3">
         <v>46190</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F7">
         <v>20.16</v>
       </c>
-      <c r="G7" s="1">
-        <v>0.66</v>
+      <c r="G7" t="s">
+        <v>31</v>
       </c>
       <c r="H7">
+        <v>0.66</v>
+      </c>
+      <c r="I7" s="1">
         <v>13.31</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>0.67</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>13.51</v>
       </c>
-      <c r="K7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7" t="s">
+        <v>36</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="3">
         <v>46191</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F8">
         <v>24.26</v>
       </c>
-      <c r="G8" s="1">
-        <v>0.65</v>
+      <c r="G8" t="s">
+        <v>31</v>
       </c>
       <c r="H8">
+        <v>0.65</v>
+      </c>
+      <c r="I8" s="1">
         <v>15.77</v>
       </c>
-      <c r="I8" s="1">
-        <v>0.66</v>
-      </c>
       <c r="J8">
+        <v>0.66</v>
+      </c>
+      <c r="K8" s="1">
         <v>16.01</v>
       </c>
-      <c r="K8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="L8" t="s">
+        <v>37</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="3">
         <v>46191</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F9">
         <v>30.92</v>
       </c>
-      <c r="G9" s="1">
-        <v>0.65</v>
+      <c r="G9" t="s">
+        <v>31</v>
       </c>
       <c r="H9">
+        <v>0.65</v>
+      </c>
+      <c r="I9" s="1">
         <v>20.1</v>
       </c>
-      <c r="I9" s="1">
-        <v>0.66</v>
-      </c>
       <c r="J9">
+        <v>0.66</v>
+      </c>
+      <c r="K9" s="1">
         <v>20.41</v>
       </c>
-      <c r="K9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="L9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="3">
         <v>46192</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E10" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F10">
         <v>24.03</v>
       </c>
-      <c r="G10" s="1">
-        <v>0.65</v>
+      <c r="G10" t="s">
+        <v>31</v>
       </c>
       <c r="H10">
+        <v>0.65</v>
+      </c>
+      <c r="I10" s="1">
         <v>15.62</v>
       </c>
-      <c r="I10" s="1">
-        <v>0.66</v>
-      </c>
       <c r="J10">
+        <v>0.66</v>
+      </c>
+      <c r="K10" s="1">
         <v>15.86</v>
       </c>
-      <c r="K10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="L10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="3">
         <v>46193</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E11" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F11">
         <v>30.11</v>
       </c>
-      <c r="G11" s="1">
-        <v>0.65</v>
+      <c r="G11" t="s">
+        <v>31</v>
       </c>
       <c r="H11">
+        <v>0.65</v>
+      </c>
+      <c r="I11" s="1">
         <v>19.57</v>
       </c>
-      <c r="I11" s="1">
-        <v>0.66</v>
-      </c>
       <c r="J11">
+        <v>0.66</v>
+      </c>
+      <c r="K11" s="1">
         <v>19.87</v>
       </c>
-      <c r="K11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="L11" t="s">
+        <v>34</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="3">
         <v>46193</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F12">
         <v>19.55</v>
       </c>
-      <c r="G12" s="1">
-        <v>0.65</v>
+      <c r="G12" t="s">
+        <v>31</v>
       </c>
       <c r="H12">
+        <v>0.65</v>
+      </c>
+      <c r="I12" s="1">
         <v>12.71</v>
       </c>
-      <c r="I12" s="1">
-        <v>0.66</v>
-      </c>
       <c r="J12">
+        <v>0.66</v>
+      </c>
+      <c r="K12" s="1">
         <v>12.9</v>
       </c>
-      <c r="K12" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="L12" t="s">
+        <v>40</v>
+      </c>
+      <c r="M12">
+        <v>188804</v>
+      </c>
+      <c r="N12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="3">
         <v>46194</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E13" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F13">
         <v>27.26</v>
       </c>
-      <c r="G13" s="1">
-        <v>0.65</v>
+      <c r="G13" t="s">
+        <v>31</v>
       </c>
       <c r="H13">
+        <v>0.65</v>
+      </c>
+      <c r="I13" s="1">
         <v>17.72</v>
       </c>
-      <c r="I13" s="1">
-        <v>0.66</v>
-      </c>
       <c r="J13">
+        <v>0.66</v>
+      </c>
+      <c r="K13" s="1">
         <v>17.99</v>
       </c>
-      <c r="K13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="L13" t="s">
+        <v>41</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="3">
         <v>46194</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E14" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F14">
         <v>19.42</v>
       </c>
-      <c r="G14" s="1">
-        <v>0.65</v>
+      <c r="G14" t="s">
+        <v>31</v>
       </c>
       <c r="H14">
+        <v>0.65</v>
+      </c>
+      <c r="I14" s="1">
         <v>12.62</v>
       </c>
-      <c r="I14" s="1">
-        <v>0.66</v>
-      </c>
       <c r="J14">
+        <v>0.66</v>
+      </c>
+      <c r="K14" s="1">
         <v>12.82</v>
       </c>
-      <c r="K14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="L14" t="s">
+        <v>42</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="3">
         <v>46195</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D15" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E15" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F15">
         <v>21.11</v>
       </c>
-      <c r="G15" s="1">
-        <v>0.65</v>
+      <c r="G15" t="s">
+        <v>31</v>
       </c>
       <c r="H15">
+        <v>0.65</v>
+      </c>
+      <c r="I15" s="1">
         <v>13.72</v>
       </c>
-      <c r="I15" s="1">
-        <v>0.66</v>
-      </c>
       <c r="J15">
+        <v>0.66</v>
+      </c>
+      <c r="K15" s="1">
         <v>13.93</v>
       </c>
-      <c r="K15" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="L15" t="s">
+        <v>43</v>
+      </c>
+      <c r="M15">
+        <v>154414</v>
+      </c>
+      <c r="N15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="3">
         <v>46195</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D16" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E16" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F16">
         <v>24.65</v>
       </c>
-      <c r="G16" s="1">
-        <v>0.65</v>
+      <c r="G16" t="s">
+        <v>31</v>
       </c>
       <c r="H16">
+        <v>0.65</v>
+      </c>
+      <c r="I16" s="1">
         <v>16.02</v>
       </c>
-      <c r="I16" s="1">
-        <v>0.66</v>
-      </c>
       <c r="J16">
+        <v>0.66</v>
+      </c>
+      <c r="K16" s="1">
         <v>16.27</v>
       </c>
-      <c r="K16" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="L16" t="s">
+        <v>44</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="3">
         <v>46195</v>
       </c>
       <c r="B17" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E17" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F17">
         <v>23.76</v>
       </c>
-      <c r="G17" s="1">
-        <v>0.65</v>
+      <c r="G17" t="s">
+        <v>31</v>
       </c>
       <c r="H17">
+        <v>0.65</v>
+      </c>
+      <c r="I17" s="1">
         <v>15.44</v>
       </c>
-      <c r="I17" s="1">
-        <v>0.66</v>
-      </c>
       <c r="J17">
+        <v>0.66</v>
+      </c>
+      <c r="K17" s="1">
         <v>15.68</v>
       </c>
-      <c r="K17" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="L17" t="s">
+        <v>45</v>
+      </c>
+      <c r="M17">
+        <v>210384</v>
+      </c>
+      <c r="N17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="3">
         <v>46196</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D18" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E18" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F18">
         <v>30.7</v>
       </c>
-      <c r="G18" s="1">
-        <v>0.65</v>
+      <c r="G18" t="s">
+        <v>31</v>
       </c>
       <c r="H18">
+        <v>0.65</v>
+      </c>
+      <c r="I18" s="1">
         <v>19.96</v>
       </c>
-      <c r="I18" s="1">
-        <v>0.66</v>
-      </c>
       <c r="J18">
+        <v>0.66</v>
+      </c>
+      <c r="K18" s="1">
         <v>20.26</v>
       </c>
-      <c r="K18" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+      <c r="L18" t="s">
+        <v>46</v>
+      </c>
+      <c r="M18">
+        <v>196189</v>
+      </c>
+      <c r="N18" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" s="3">
         <v>46197</v>
       </c>
       <c r="B19" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E19" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F19">
-        <v>22.48</v>
-      </c>
-      <c r="G19" s="1">
-        <v>0.65</v>
+        <v>31.86</v>
+      </c>
+      <c r="G19" t="s">
+        <v>31</v>
       </c>
       <c r="H19">
-        <v>14.61</v>
+        <v>0.65</v>
       </c>
       <c r="I19" s="1">
-        <v>0.66</v>
+        <v>20.71</v>
       </c>
       <c r="J19">
-        <v>14.84</v>
-      </c>
-      <c r="K19" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+        <v>0.66</v>
+      </c>
+      <c r="K19" s="1">
+        <v>21.03</v>
+      </c>
+      <c r="L19" t="s">
+        <v>47</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="3">
         <v>46197</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D20" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E20" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F20">
-        <v>31.86</v>
-      </c>
-      <c r="G20" s="1">
-        <v>0.65</v>
+        <v>19.92</v>
+      </c>
+      <c r="G20" t="s">
+        <v>31</v>
       </c>
       <c r="H20">
-        <v>20.71</v>
+        <v>0.65</v>
       </c>
       <c r="I20" s="1">
-        <v>0.66</v>
+        <v>12.95</v>
       </c>
       <c r="J20">
-        <v>21.03</v>
-      </c>
-      <c r="K20" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+        <v>0.66</v>
+      </c>
+      <c r="K20" s="1">
+        <v>13.15</v>
+      </c>
+      <c r="L20" t="s">
+        <v>48</v>
+      </c>
+      <c r="M20">
+        <v>154523</v>
+      </c>
+      <c r="N20" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="3">
         <v>46197</v>
       </c>
       <c r="B21" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C21" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E21" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F21">
-        <v>19.92</v>
-      </c>
-      <c r="G21" s="1">
-        <v>0.65</v>
+        <v>22.48</v>
+      </c>
+      <c r="G21" t="s">
+        <v>31</v>
       </c>
       <c r="H21">
-        <v>12.95</v>
+        <v>0.65</v>
       </c>
       <c r="I21" s="1">
-        <v>0.66</v>
+        <v>14.61</v>
       </c>
       <c r="J21">
-        <v>13.15</v>
-      </c>
-      <c r="K21" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+        <v>0.66</v>
+      </c>
+      <c r="K21" s="1">
+        <v>14.84</v>
+      </c>
+      <c r="L21" t="s">
+        <v>49</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" s="3">
         <v>46197</v>
       </c>
       <c r="B22" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D22" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E22" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F22">
         <v>18.58</v>
       </c>
-      <c r="G22" s="1">
-        <v>0.65</v>
+      <c r="G22" t="s">
+        <v>31</v>
       </c>
       <c r="H22">
+        <v>0.65</v>
+      </c>
+      <c r="I22" s="1">
         <v>12.08</v>
       </c>
-      <c r="I22" s="1">
-        <v>0.66</v>
-      </c>
       <c r="J22">
+        <v>0.66</v>
+      </c>
+      <c r="K22" s="1">
         <v>12.26</v>
       </c>
-      <c r="K22" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
+      <c r="L22" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22">
+        <v>196288</v>
+      </c>
+      <c r="N22" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" s="3">
         <v>46198</v>
       </c>
       <c r="B23" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D23" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E23" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F23">
         <v>24.27</v>
       </c>
-      <c r="G23" s="1">
-        <v>0.65</v>
+      <c r="G23" t="s">
+        <v>31</v>
       </c>
       <c r="H23">
+        <v>0.65</v>
+      </c>
+      <c r="I23" s="1">
         <v>15.78</v>
       </c>
-      <c r="I23" s="1">
-        <v>0.66</v>
-      </c>
       <c r="J23">
+        <v>0.66</v>
+      </c>
+      <c r="K23" s="1">
         <v>16.02</v>
       </c>
-      <c r="K23" t="s">
+      <c r="L23" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="24" spans="1:11">
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="3">
         <v>46198</v>
       </c>
       <c r="B24" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C24" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D24" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E24" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F24">
         <v>20.82</v>
       </c>
-      <c r="G24" s="1">
-        <v>0.65</v>
+      <c r="G24" t="s">
+        <v>31</v>
       </c>
       <c r="H24">
+        <v>0.65</v>
+      </c>
+      <c r="I24" s="1">
         <v>13.53</v>
       </c>
-      <c r="I24" s="1">
-        <v>0.66</v>
-      </c>
       <c r="J24">
+        <v>0.66</v>
+      </c>
+      <c r="K24" s="1">
         <v>13.74</v>
       </c>
-      <c r="K24" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" s="4" t="s">
+      <c r="L24" t="s">
         <v>51</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="A28" s="5" t="s">
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" t="s">
+        <v>29</v>
+      </c>
+      <c r="E25" t="s">
+        <v>30</v>
+      </c>
+      <c r="F25">
+        <v>21.58</v>
+      </c>
+      <c r="G25" t="s">
+        <v>31</v>
+      </c>
+      <c r="H25">
+        <v>0.65</v>
+      </c>
+      <c r="I25" s="1">
+        <v>14.03</v>
+      </c>
+      <c r="J25">
+        <v>0.66</v>
+      </c>
+      <c r="K25" s="1">
+        <v>14.24</v>
+      </c>
+      <c r="L25" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" t="s">
+        <v>21</v>
+      </c>
+      <c r="D26" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" t="s">
+        <v>30</v>
+      </c>
+      <c r="F26">
+        <v>18.48</v>
+      </c>
+      <c r="G26" t="s">
+        <v>31</v>
+      </c>
+      <c r="H26">
+        <v>0.65</v>
+      </c>
+      <c r="I26" s="1">
+        <v>12.01</v>
+      </c>
+      <c r="J26">
+        <v>0.66</v>
+      </c>
+      <c r="K26" s="1">
+        <v>12.2</v>
+      </c>
+      <c r="L26" t="s">
         <v>53</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" s="3">
+        <v>46200</v>
+      </c>
+      <c r="B27" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27" t="s">
+        <v>30</v>
+      </c>
+      <c r="F27">
+        <v>30.41</v>
+      </c>
+      <c r="G27" t="s">
+        <v>31</v>
+      </c>
+      <c r="H27">
+        <v>0.65</v>
+      </c>
+      <c r="I27" s="1">
+        <v>19.77</v>
+      </c>
+      <c r="J27">
+        <v>0.66</v>
+      </c>
+      <c r="K27" s="1">
+        <v>20.07</v>
+      </c>
+      <c r="L27" t="s">
         <v>54</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="M27">
+        <v>210845</v>
+      </c>
+      <c r="N27" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="3">
+        <v>46200</v>
+      </c>
+      <c r="B28" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" t="s">
+        <v>30</v>
+      </c>
+      <c r="F28">
+        <v>22.23</v>
+      </c>
+      <c r="G28" t="s">
+        <v>31</v>
+      </c>
+      <c r="H28">
+        <v>0.65</v>
+      </c>
+      <c r="I28" s="1">
+        <v>14.45</v>
+      </c>
+      <c r="J28">
+        <v>0.66</v>
+      </c>
+      <c r="K28" s="1">
+        <v>14.67</v>
+      </c>
+      <c r="L28" t="s">
         <v>55</v>
       </c>
-      <c r="E28" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
-      <c r="A29" s="6" t="s">
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" s="3">
+        <v>46201</v>
+      </c>
+      <c r="B29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" t="s">
+        <v>29</v>
+      </c>
+      <c r="E29" t="s">
+        <v>30</v>
+      </c>
+      <c r="F29">
+        <v>23.11</v>
+      </c>
+      <c r="G29" t="s">
+        <v>31</v>
+      </c>
+      <c r="H29">
+        <v>0.65</v>
+      </c>
+      <c r="I29" s="1">
+        <v>15.02</v>
+      </c>
+      <c r="J29">
+        <v>0.66</v>
+      </c>
+      <c r="K29" s="1">
+        <v>15.25</v>
+      </c>
+      <c r="L29" t="s">
+        <v>56</v>
+      </c>
+      <c r="M29">
+        <v>196489</v>
+      </c>
+      <c r="N29" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="3">
+        <v>46201</v>
+      </c>
+      <c r="B30" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" t="s">
+        <v>30</v>
+      </c>
+      <c r="F30">
+        <v>21.32</v>
+      </c>
+      <c r="G30" t="s">
+        <v>31</v>
+      </c>
+      <c r="H30">
+        <v>0.65</v>
+      </c>
+      <c r="I30" s="1">
+        <v>13.86</v>
+      </c>
+      <c r="J30">
+        <v>0.66</v>
+      </c>
+      <c r="K30" s="1">
+        <v>14.07</v>
+      </c>
+      <c r="L30" t="s">
+        <v>57</v>
+      </c>
+      <c r="M30">
+        <v>189359</v>
+      </c>
+      <c r="N30" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="3">
+        <v>46201</v>
+      </c>
+      <c r="B31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" t="s">
+        <v>30</v>
+      </c>
+      <c r="F31">
+        <v>23.7</v>
+      </c>
+      <c r="G31" t="s">
+        <v>31</v>
+      </c>
+      <c r="H31">
+        <v>0.65</v>
+      </c>
+      <c r="I31" s="1">
+        <v>15.4</v>
+      </c>
+      <c r="J31">
+        <v>0.66</v>
+      </c>
+      <c r="K31" s="1">
+        <v>15.64</v>
+      </c>
+      <c r="L31" t="s">
+        <v>58</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B32" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" t="s">
+        <v>22</v>
+      </c>
+      <c r="D32" t="s">
+        <v>28</v>
+      </c>
+      <c r="E32" t="s">
+        <v>30</v>
+      </c>
+      <c r="F32">
+        <v>23.11</v>
+      </c>
+      <c r="G32" t="s">
+        <v>31</v>
+      </c>
+      <c r="H32">
+        <v>0.65</v>
+      </c>
+      <c r="I32" s="1">
+        <v>15.02</v>
+      </c>
+      <c r="J32">
+        <v>0.66</v>
+      </c>
+      <c r="K32" s="1">
+        <v>15.25</v>
+      </c>
+      <c r="L32" t="s">
+        <v>59</v>
+      </c>
+      <c r="M32">
+        <v>178788</v>
+      </c>
+      <c r="N32" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="A33" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" t="s">
         <v>27</v>
       </c>
-      <c r="B29" s="7">
-        <v>574.27</v>
-      </c>
-      <c r="C29" s="7">
-        <v>23</v>
-      </c>
-      <c r="D29" s="8">
-        <v>0.6539</v>
-      </c>
-      <c r="E29" s="7">
-        <v>375.51</v>
-      </c>
-      <c r="F29" s="7">
-        <v>381.25</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
-      <c r="A30" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B30" s="10">
-        <v>574.27</v>
-      </c>
-      <c r="C30" s="10">
-        <v>23</v>
-      </c>
-      <c r="D30" s="8"/>
-      <c r="E30" s="10">
-        <v>375.51</v>
-      </c>
-      <c r="F30" s="10">
-        <v>381.25</v>
+      <c r="E33" t="s">
+        <v>30</v>
+      </c>
+      <c r="F33">
+        <v>30.73</v>
+      </c>
+      <c r="G33" t="s">
+        <v>31</v>
+      </c>
+      <c r="H33">
+        <v>0.65</v>
+      </c>
+      <c r="I33" s="1">
+        <v>19.97</v>
+      </c>
+      <c r="J33">
+        <v>0.66</v>
+      </c>
+      <c r="K33" s="1">
+        <v>20.28</v>
+      </c>
+      <c r="L33" t="s">
+        <v>60</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B34" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" t="s">
+        <v>30</v>
+      </c>
+      <c r="F34">
+        <v>28.27</v>
+      </c>
+      <c r="G34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H34">
+        <v>0.65</v>
+      </c>
+      <c r="I34" s="1">
+        <v>18.38</v>
+      </c>
+      <c r="J34">
+        <v>0.66</v>
+      </c>
+      <c r="K34" s="1">
+        <v>18.66</v>
+      </c>
+      <c r="L34" t="s">
+        <v>61</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" t="s">
+        <v>30</v>
+      </c>
+      <c r="F35">
+        <v>21.56</v>
+      </c>
+      <c r="G35" t="s">
+        <v>31</v>
+      </c>
+      <c r="H35">
+        <v>0.65</v>
+      </c>
+      <c r="I35" s="1">
+        <v>14.01</v>
+      </c>
+      <c r="J35">
+        <v>0.66</v>
+      </c>
+      <c r="K35" s="1">
+        <v>14.23</v>
+      </c>
+      <c r="L35" t="s">
+        <v>62</v>
+      </c>
+      <c r="M35">
+        <v>189496</v>
+      </c>
+      <c r="N35" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B36" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" t="s">
+        <v>30</v>
+      </c>
+      <c r="F36">
+        <v>27.73</v>
+      </c>
+      <c r="G36" t="s">
+        <v>31</v>
+      </c>
+      <c r="H36">
+        <v>0.65</v>
+      </c>
+      <c r="I36" s="1">
+        <v>18.02</v>
+      </c>
+      <c r="J36">
+        <v>0.66</v>
+      </c>
+      <c r="K36" s="1">
+        <v>18.3</v>
+      </c>
+      <c r="L36" t="s">
+        <v>63</v>
+      </c>
+      <c r="M36">
+        <v>211231</v>
+      </c>
+      <c r="N36" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B41" s="7">
+        <v>866.5</v>
+      </c>
+      <c r="C41" s="7">
+        <v>35</v>
+      </c>
+      <c r="D41" s="8">
+        <v>0.6526</v>
+      </c>
+      <c r="E41" s="7">
+        <v>565.45</v>
+      </c>
+      <c r="F41" s="7">
+        <v>574.11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
+      <c r="A42" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B42" s="10">
+        <v>866.5</v>
+      </c>
+      <c r="C42" s="10">
+        <v>35</v>
+      </c>
+      <c r="D42" s="8"/>
+      <c r="E42" s="10">
+        <v>565.45</v>
+      </c>
+      <c r="F42" s="10">
+        <v>574.11</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A39:F39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ/ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ/ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="69">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,27 +55,27 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1148 Варна пристанище</t>
-  </si>
-  <si>
-    <t>1158 Варна Чайка</t>
-  </si>
-  <si>
-    <t>1146 Варна Сливница</t>
-  </si>
-  <si>
-    <t>1911 O5 Варна</t>
+    <t>Варна Чайка</t>
+  </si>
+  <si>
+    <t>Варна Порт</t>
+  </si>
+  <si>
+    <t>Варна Сливница</t>
+  </si>
+  <si>
+    <t>Варна</t>
+  </si>
+  <si>
+    <t>В8977ВР</t>
+  </si>
+  <si>
+    <t>В7237ВР</t>
   </si>
   <si>
     <t>В8971ВР</t>
   </si>
   <si>
-    <t>В7237ВР</t>
-  </si>
-  <si>
-    <t>В8977ВР</t>
-  </si>
-  <si>
     <t>В8991ВР</t>
   </si>
   <si>
@@ -88,15 +85,15 @@
     <t>В8982ВР</t>
   </si>
   <si>
+    <t>78970155027722481</t>
+  </si>
+  <si>
+    <t>78970155027722465</t>
+  </si>
+  <si>
     <t>78970155027722473</t>
   </si>
   <si>
-    <t>78970155027722465</t>
-  </si>
-  <si>
-    <t>78970155027722481</t>
-  </si>
-  <si>
     <t>78970155027722515</t>
   </si>
   <si>
@@ -109,208 +106,103 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>11:44:00</t>
-  </si>
-  <si>
-    <t>07:03:00</t>
-  </si>
-  <si>
-    <t>09:07:00</t>
-  </si>
-  <si>
-    <t>14:01:00</t>
-  </si>
-  <si>
-    <t>20:37:00</t>
-  </si>
-  <si>
-    <t>09:56:00</t>
-  </si>
-  <si>
-    <t>19:36:00</t>
-  </si>
-  <si>
-    <t>18:34:00</t>
-  </si>
-  <si>
-    <t>10:19:00</t>
-  </si>
-  <si>
-    <t>13:30:00</t>
-  </si>
-  <si>
-    <t>20:29:00</t>
-  </si>
-  <si>
-    <t>10:33:00</t>
-  </si>
-  <si>
-    <t>13:25:00</t>
-  </si>
-  <si>
-    <t>18:19:00</t>
-  </si>
-  <si>
-    <t>15:13:00</t>
-  </si>
-  <si>
-    <t>08:38:00</t>
-  </si>
-  <si>
-    <t>10:35:00</t>
-  </si>
-  <si>
-    <t>07:18:00</t>
-  </si>
-  <si>
-    <t>19:08:00</t>
-  </si>
-  <si>
-    <t>08:45:00</t>
-  </si>
-  <si>
-    <t>18:41:00</t>
-  </si>
-  <si>
-    <t>06:53:00</t>
-  </si>
-  <si>
-    <t>09:20:00</t>
-  </si>
-  <si>
-    <t>08:25:00</t>
-  </si>
-  <si>
-    <t>14:45:00</t>
-  </si>
-  <si>
-    <t>21:08:00</t>
-  </si>
-  <si>
-    <t>08:35:00</t>
-  </si>
-  <si>
-    <t>08:40:00</t>
-  </si>
-  <si>
-    <t>10:29:00</t>
-  </si>
-  <si>
-    <t>18:16:00</t>
-  </si>
-  <si>
-    <t>14:33:00</t>
-  </si>
-  <si>
-    <t>19:15:00</t>
-  </si>
-  <si>
-    <t>3233437605 3233437605</t>
-  </si>
-  <si>
-    <t>3233411429 3233411429</t>
-  </si>
-  <si>
-    <t>3233411735 3233411735</t>
-  </si>
-  <si>
-    <t>3233485135 3233485135</t>
-  </si>
-  <si>
-    <t>3233490809 3233490809</t>
-  </si>
-  <si>
-    <t>3233495918 3233495918</t>
-  </si>
-  <si>
-    <t>3233529758 3233529758</t>
-  </si>
-  <si>
-    <t>3233542645 3233542645</t>
-  </si>
-  <si>
-    <t>3233595294 3233595294</t>
-  </si>
-  <si>
-    <t>3233637719 3233637719</t>
-  </si>
-  <si>
-    <t>3233607682 3233607682</t>
-  </si>
-  <si>
-    <t>3233674186 3233674186</t>
-  </si>
-  <si>
-    <t>3233692116 3233692116</t>
-  </si>
-  <si>
-    <t>3233710348 3233710348</t>
-  </si>
-  <si>
-    <t>3233722381 3233722381</t>
-  </si>
-  <si>
-    <t>3233731832 3233731832</t>
-  </si>
-  <si>
-    <t>3233767434 3233767434</t>
-  </si>
-  <si>
-    <t>3233782618 3233782618</t>
-  </si>
-  <si>
-    <t>3233805885 3233805885</t>
-  </si>
-  <si>
-    <t>3233808756 3233808756</t>
-  </si>
-  <si>
-    <t>3233808884 3233808884</t>
-  </si>
-  <si>
-    <t>3233854796 3233854796</t>
-  </si>
-  <si>
-    <t>3233855250 3233855250</t>
-  </si>
-  <si>
-    <t>3233950927 3233950927</t>
-  </si>
-  <si>
-    <t>3233872590 3233872590</t>
-  </si>
-  <si>
-    <t>3233945380 3233945380</t>
-  </si>
-  <si>
-    <t>3233945924 3233945924</t>
-  </si>
-  <si>
-    <t>3234013256 3234013256</t>
-  </si>
-  <si>
-    <t>3234020956 3234020956</t>
-  </si>
-  <si>
-    <t>3233998895 3233998895</t>
-  </si>
-  <si>
-    <t>3234049845 3234049845</t>
-  </si>
-  <si>
-    <t>3234051279 3234051279</t>
-  </si>
-  <si>
-    <t>3234057743 3234057743</t>
-  </si>
-  <si>
-    <t>3234100173 3234100173</t>
-  </si>
-  <si>
-    <t>3234098478 3234098478</t>
+    <t>07:03</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>09:07</t>
+  </si>
+  <si>
+    <t>14:01</t>
+  </si>
+  <si>
+    <t>20:37</t>
+  </si>
+  <si>
+    <t>09:56</t>
+  </si>
+  <si>
+    <t>19:36</t>
+  </si>
+  <si>
+    <t>18:35</t>
+  </si>
+  <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>10:33</t>
+  </si>
+  <si>
+    <t>13:26</t>
+  </si>
+  <si>
+    <t>18:20</t>
+  </si>
+  <si>
+    <t>15:13</t>
+  </si>
+  <si>
+    <t>07:19</t>
+  </si>
+  <si>
+    <t>08:39</t>
+  </si>
+  <si>
+    <t>10:36</t>
+  </si>
+  <si>
+    <t>19:08</t>
+  </si>
+  <si>
+    <t>07:18</t>
+  </si>
+  <si>
+    <t>08:45</t>
+  </si>
+  <si>
+    <t>06:53</t>
+  </si>
+  <si>
+    <t>18:41</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>09:20</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>21:08</t>
+  </si>
+  <si>
+    <t>08:41</t>
+  </si>
+  <si>
+    <t>10:29</t>
+  </si>
+  <si>
+    <t>18:16</t>
+  </si>
+  <si>
+    <t>14:33</t>
+  </si>
+  <si>
+    <t>19:16</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ</t>
@@ -730,7 +622,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N42"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -739,17 +631,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -789,143 +680,131 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46189</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2">
+        <v>26.4</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="H2">
+        <v>17.69</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="J2">
+        <v>17.95</v>
+      </c>
+      <c r="K2" t="s">
         <v>30</v>
       </c>
-      <c r="F2">
-        <v>21.55</v>
-      </c>
-      <c r="G2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H2">
-        <v>0.66</v>
-      </c>
-      <c r="I2" s="1">
-        <v>14.22</v>
-      </c>
-      <c r="J2">
-        <v>0.67</v>
-      </c>
-      <c r="K2" s="1">
-        <v>14.44</v>
-      </c>
-      <c r="L2" t="s">
-        <v>32</v>
+      <c r="L2">
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>188337</v>
-      </c>
-      <c r="N2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>113649</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46189</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F3">
         <v>36.37</v>
       </c>
-      <c r="G3" t="s">
-        <v>31</v>
+      <c r="G3" s="1">
+        <v>0.67</v>
       </c>
       <c r="H3">
-        <v>0.67</v>
+        <v>24.37</v>
       </c>
       <c r="I3" s="1">
-        <v>24.37</v>
+        <v>0.68</v>
       </c>
       <c r="J3">
-        <v>0.68</v>
-      </c>
-      <c r="K3" s="1">
         <v>24.73</v>
       </c>
-      <c r="L3" t="s">
-        <v>33</v>
+      <c r="K3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>113651</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46189</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F4">
-        <v>26.4</v>
-      </c>
-      <c r="G4" t="s">
+        <v>21.55</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="H4">
+        <v>14.22</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="J4">
+        <v>14.44</v>
+      </c>
+      <c r="K4" t="s">
         <v>31</v>
       </c>
-      <c r="H4">
-        <v>0.67</v>
-      </c>
-      <c r="I4" s="1">
-        <v>17.69</v>
-      </c>
-      <c r="J4">
-        <v>0.68</v>
-      </c>
-      <c r="K4" s="1">
-        <v>17.95</v>
-      </c>
-      <c r="L4" t="s">
-        <v>33</v>
+      <c r="L4">
+        <v>188337</v>
       </c>
       <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>219804</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
         <v>46190</v>
       </c>
@@ -933,43 +812,40 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F5">
         <v>30.84</v>
       </c>
-      <c r="G5" t="s">
-        <v>31</v>
+      <c r="G5" s="1">
+        <v>0.66</v>
       </c>
       <c r="H5">
-        <v>0.66</v>
+        <v>20.35</v>
       </c>
       <c r="I5" s="1">
-        <v>20.35</v>
+        <v>0.67</v>
       </c>
       <c r="J5">
-        <v>0.67</v>
-      </c>
-      <c r="K5" s="1">
         <v>20.66</v>
       </c>
-      <c r="L5" t="s">
-        <v>34</v>
+      <c r="K5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>220176</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="3">
         <v>46190</v>
       </c>
@@ -977,87 +853,81 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F6">
         <v>25.25</v>
       </c>
-      <c r="G6" t="s">
-        <v>31</v>
+      <c r="G6" s="1">
+        <v>0.66</v>
       </c>
       <c r="H6">
-        <v>0.66</v>
+        <v>16.66</v>
       </c>
       <c r="I6" s="1">
-        <v>16.66</v>
+        <v>0.67</v>
       </c>
       <c r="J6">
-        <v>0.67</v>
-      </c>
-      <c r="K6" s="1">
         <v>16.92</v>
       </c>
-      <c r="L6" t="s">
-        <v>35</v>
+      <c r="K6" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
       </c>
       <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>220310</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="3">
         <v>46190</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F7">
         <v>20.16</v>
       </c>
-      <c r="G7" t="s">
-        <v>31</v>
+      <c r="G7" s="1">
+        <v>0.66</v>
       </c>
       <c r="H7">
-        <v>0.66</v>
+        <v>13.31</v>
       </c>
       <c r="I7" s="1">
-        <v>13.31</v>
+        <v>0.67</v>
       </c>
       <c r="J7">
-        <v>0.67</v>
-      </c>
-      <c r="K7" s="1">
         <v>13.51</v>
       </c>
-      <c r="L7" t="s">
-        <v>36</v>
+      <c r="K7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
       </c>
       <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>114655</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="3">
         <v>46191</v>
       </c>
@@ -1065,87 +935,81 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F8">
         <v>24.26</v>
       </c>
-      <c r="G8" t="s">
-        <v>31</v>
+      <c r="G8" s="1">
+        <v>0.65</v>
       </c>
       <c r="H8">
-        <v>0.65</v>
+        <v>15.77</v>
       </c>
       <c r="I8" s="1">
-        <v>15.77</v>
+        <v>0.66</v>
       </c>
       <c r="J8">
-        <v>0.66</v>
-      </c>
-      <c r="K8" s="1">
         <v>16.01</v>
       </c>
-      <c r="L8" t="s">
-        <v>37</v>
+      <c r="K8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
       </c>
       <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+        <v>220589</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="3">
         <v>46191</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F9">
         <v>30.92</v>
       </c>
-      <c r="G9" t="s">
-        <v>31</v>
+      <c r="G9" s="1">
+        <v>0.65</v>
       </c>
       <c r="H9">
-        <v>0.65</v>
+        <v>20.1</v>
       </c>
       <c r="I9" s="1">
-        <v>20.1</v>
+        <v>0.66</v>
       </c>
       <c r="J9">
-        <v>0.66</v>
-      </c>
-      <c r="K9" s="1">
         <v>20.41</v>
       </c>
-      <c r="L9" t="s">
-        <v>38</v>
+      <c r="K9" t="s">
+        <v>36</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
       </c>
       <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>115188</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="3">
         <v>46192</v>
       </c>
@@ -1153,43 +1017,40 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F10">
         <v>24.03</v>
       </c>
-      <c r="G10" t="s">
-        <v>31</v>
+      <c r="G10" s="1">
+        <v>0.65</v>
       </c>
       <c r="H10">
-        <v>0.65</v>
+        <v>15.62</v>
       </c>
       <c r="I10" s="1">
-        <v>15.62</v>
+        <v>0.66</v>
       </c>
       <c r="J10">
-        <v>0.66</v>
-      </c>
-      <c r="K10" s="1">
         <v>15.86</v>
       </c>
-      <c r="L10" t="s">
-        <v>39</v>
+      <c r="K10" t="s">
+        <v>37</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
       </c>
       <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>221484</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="3">
         <v>46193</v>
       </c>
@@ -1197,87 +1058,81 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F11">
         <v>30.11</v>
       </c>
-      <c r="G11" t="s">
-        <v>31</v>
+      <c r="G11" s="1">
+        <v>0.65</v>
       </c>
       <c r="H11">
-        <v>0.65</v>
+        <v>19.57</v>
       </c>
       <c r="I11" s="1">
-        <v>19.57</v>
+        <v>0.66</v>
       </c>
       <c r="J11">
-        <v>0.66</v>
-      </c>
-      <c r="K11" s="1">
         <v>19.87</v>
       </c>
-      <c r="L11" t="s">
-        <v>34</v>
+      <c r="K11" t="s">
+        <v>32</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
       </c>
       <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>221594</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="3">
         <v>46193</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F12">
         <v>19.55</v>
       </c>
-      <c r="G12" t="s">
-        <v>31</v>
+      <c r="G12" s="1">
+        <v>0.65</v>
       </c>
       <c r="H12">
-        <v>0.65</v>
+        <v>12.71</v>
       </c>
       <c r="I12" s="1">
-        <v>12.71</v>
+        <v>0.66</v>
       </c>
       <c r="J12">
-        <v>0.66</v>
-      </c>
-      <c r="K12" s="1">
         <v>12.9</v>
       </c>
-      <c r="L12" t="s">
-        <v>40</v>
+      <c r="K12" t="s">
+        <v>38</v>
+      </c>
+      <c r="L12">
+        <v>188804</v>
       </c>
       <c r="M12">
-        <v>188804</v>
-      </c>
-      <c r="N12" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+        <v>115949</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="3">
         <v>46194</v>
       </c>
@@ -1285,131 +1140,122 @@
         <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F13">
         <v>27.26</v>
       </c>
-      <c r="G13" t="s">
-        <v>31</v>
+      <c r="G13" s="1">
+        <v>0.65</v>
       </c>
       <c r="H13">
-        <v>0.65</v>
+        <v>17.72</v>
       </c>
       <c r="I13" s="1">
-        <v>17.72</v>
+        <v>0.66</v>
       </c>
       <c r="J13">
-        <v>0.66</v>
-      </c>
-      <c r="K13" s="1">
         <v>17.99</v>
       </c>
-      <c r="L13" t="s">
-        <v>41</v>
+      <c r="K13" t="s">
+        <v>39</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
       </c>
       <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+        <v>222032</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="3">
         <v>46194</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F14">
         <v>19.42</v>
       </c>
-      <c r="G14" t="s">
-        <v>31</v>
+      <c r="G14" s="1">
+        <v>0.65</v>
       </c>
       <c r="H14">
-        <v>0.65</v>
+        <v>12.62</v>
       </c>
       <c r="I14" s="1">
-        <v>12.62</v>
+        <v>0.66</v>
       </c>
       <c r="J14">
-        <v>0.66</v>
-      </c>
-      <c r="K14" s="1">
         <v>12.82</v>
       </c>
-      <c r="L14" t="s">
-        <v>42</v>
+      <c r="K14" t="s">
+        <v>40</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
       </c>
       <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+        <v>116798</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="3">
         <v>46195</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F15">
         <v>21.11</v>
       </c>
-      <c r="G15" t="s">
-        <v>31</v>
+      <c r="G15" s="1">
+        <v>0.65</v>
       </c>
       <c r="H15">
-        <v>0.65</v>
+        <v>13.72</v>
       </c>
       <c r="I15" s="1">
-        <v>13.72</v>
+        <v>0.66</v>
       </c>
       <c r="J15">
-        <v>0.66</v>
-      </c>
-      <c r="K15" s="1">
         <v>13.93</v>
       </c>
-      <c r="L15" t="s">
-        <v>43</v>
+      <c r="K15" t="s">
+        <v>41</v>
+      </c>
+      <c r="L15">
+        <v>154414</v>
       </c>
       <c r="M15">
-        <v>154414</v>
-      </c>
-      <c r="N15" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+        <v>144474</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="3">
         <v>46195</v>
       </c>
@@ -1417,43 +1263,40 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F16">
         <v>24.65</v>
       </c>
-      <c r="G16" t="s">
-        <v>31</v>
+      <c r="G16" s="1">
+        <v>0.65</v>
       </c>
       <c r="H16">
-        <v>0.65</v>
+        <v>16.02</v>
       </c>
       <c r="I16" s="1">
-        <v>16.02</v>
+        <v>0.66</v>
       </c>
       <c r="J16">
-        <v>0.66</v>
-      </c>
-      <c r="K16" s="1">
         <v>16.27</v>
       </c>
-      <c r="L16" t="s">
-        <v>44</v>
+      <c r="K16" t="s">
+        <v>42</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
       </c>
       <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+        <v>222430</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="3">
         <v>46195</v>
       </c>
@@ -1461,87 +1304,81 @@
         <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D17" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F17">
         <v>23.76</v>
       </c>
-      <c r="G17" t="s">
-        <v>31</v>
+      <c r="G17" s="1">
+        <v>0.65</v>
       </c>
       <c r="H17">
-        <v>0.65</v>
+        <v>15.44</v>
       </c>
       <c r="I17" s="1">
-        <v>15.44</v>
+        <v>0.66</v>
       </c>
       <c r="J17">
-        <v>0.66</v>
-      </c>
-      <c r="K17" s="1">
         <v>15.68</v>
       </c>
-      <c r="L17" t="s">
-        <v>45</v>
+      <c r="K17" t="s">
+        <v>43</v>
+      </c>
+      <c r="L17">
+        <v>210384</v>
       </c>
       <c r="M17">
-        <v>210384</v>
-      </c>
-      <c r="N17" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+        <v>222666</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="3">
         <v>46196</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F18">
         <v>30.7</v>
       </c>
-      <c r="G18" t="s">
-        <v>31</v>
+      <c r="G18" s="1">
+        <v>0.65</v>
       </c>
       <c r="H18">
-        <v>0.65</v>
+        <v>19.96</v>
       </c>
       <c r="I18" s="1">
-        <v>19.96</v>
+        <v>0.66</v>
       </c>
       <c r="J18">
-        <v>0.66</v>
-      </c>
-      <c r="K18" s="1">
         <v>20.26</v>
       </c>
-      <c r="L18" t="s">
-        <v>46</v>
+      <c r="K18" t="s">
+        <v>44</v>
+      </c>
+      <c r="L18">
+        <v>196189</v>
       </c>
       <c r="M18">
-        <v>196189</v>
-      </c>
-      <c r="N18" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
+        <v>117723</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="3">
         <v>46197</v>
       </c>
@@ -1549,43 +1386,40 @@
         <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F19">
-        <v>31.86</v>
-      </c>
-      <c r="G19" t="s">
-        <v>31</v>
+        <v>22.48</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0.65</v>
       </c>
       <c r="H19">
-        <v>0.65</v>
+        <v>14.61</v>
       </c>
       <c r="I19" s="1">
-        <v>20.71</v>
+        <v>0.66</v>
       </c>
       <c r="J19">
-        <v>0.66</v>
-      </c>
-      <c r="K19" s="1">
-        <v>21.03</v>
-      </c>
-      <c r="L19" t="s">
-        <v>47</v>
+        <v>14.84</v>
+      </c>
+      <c r="K19" t="s">
+        <v>45</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
       </c>
       <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
+        <v>223229</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="3">
         <v>46197</v>
       </c>
@@ -1593,43 +1427,40 @@
         <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F20">
-        <v>19.92</v>
-      </c>
-      <c r="G20" t="s">
-        <v>31</v>
+        <v>31.86</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0.65</v>
       </c>
       <c r="H20">
-        <v>0.65</v>
+        <v>20.71</v>
       </c>
       <c r="I20" s="1">
-        <v>12.95</v>
+        <v>0.66</v>
       </c>
       <c r="J20">
-        <v>0.66</v>
-      </c>
-      <c r="K20" s="1">
-        <v>13.15</v>
-      </c>
-      <c r="L20" t="s">
-        <v>48</v>
+        <v>21.03</v>
+      </c>
+      <c r="K20" t="s">
+        <v>46</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
       </c>
       <c r="M20">
-        <v>154523</v>
-      </c>
-      <c r="N20" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
+        <v>223261</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="3">
         <v>46197</v>
       </c>
@@ -1643,81 +1474,75 @@
         <v>26</v>
       </c>
       <c r="E21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F21">
-        <v>22.48</v>
-      </c>
-      <c r="G21" t="s">
-        <v>31</v>
+        <v>19.92</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0.65</v>
       </c>
       <c r="H21">
-        <v>0.65</v>
+        <v>12.95</v>
       </c>
       <c r="I21" s="1">
-        <v>14.61</v>
+        <v>0.66</v>
       </c>
       <c r="J21">
-        <v>0.66</v>
-      </c>
-      <c r="K21" s="1">
-        <v>14.84</v>
-      </c>
-      <c r="L21" t="s">
-        <v>49</v>
+        <v>13.15</v>
+      </c>
+      <c r="K21" t="s">
+        <v>47</v>
+      </c>
+      <c r="L21">
+        <v>154523</v>
       </c>
       <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
+        <v>223339</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="3">
         <v>46197</v>
       </c>
       <c r="B22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F22">
         <v>18.58</v>
       </c>
-      <c r="G22" t="s">
-        <v>31</v>
+      <c r="G22" s="1">
+        <v>0.65</v>
       </c>
       <c r="H22">
-        <v>0.65</v>
+        <v>12.08</v>
       </c>
       <c r="I22" s="1">
-        <v>12.08</v>
+        <v>0.66</v>
       </c>
       <c r="J22">
-        <v>0.66</v>
-      </c>
-      <c r="K22" s="1">
         <v>12.26</v>
       </c>
-      <c r="L22" t="s">
-        <v>50</v>
+      <c r="K22" t="s">
+        <v>48</v>
+      </c>
+      <c r="L22">
+        <v>196288</v>
       </c>
       <c r="M22">
-        <v>196288</v>
-      </c>
-      <c r="N22" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+        <v>120491</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" s="3">
         <v>46198</v>
       </c>
@@ -1725,527 +1550,491 @@
         <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D23" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F23">
         <v>24.27</v>
       </c>
-      <c r="G23" t="s">
-        <v>31</v>
+      <c r="G23" s="1">
+        <v>0.65</v>
       </c>
       <c r="H23">
-        <v>0.65</v>
+        <v>15.78</v>
       </c>
       <c r="I23" s="1">
-        <v>15.78</v>
+        <v>0.66</v>
       </c>
       <c r="J23">
-        <v>0.66</v>
-      </c>
-      <c r="K23" s="1">
         <v>16.02</v>
       </c>
-      <c r="L23" t="s">
+      <c r="K23" t="s">
         <v>49</v>
       </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
       <c r="M23">
-        <v>0</v>
-      </c>
-      <c r="N23" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
+        <v>223678</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" s="3">
         <v>46198</v>
       </c>
       <c r="B24" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F24">
         <v>20.82</v>
       </c>
-      <c r="G24" t="s">
-        <v>31</v>
+      <c r="G24" s="1">
+        <v>0.65</v>
       </c>
       <c r="H24">
-        <v>0.65</v>
+        <v>13.53</v>
       </c>
       <c r="I24" s="1">
-        <v>13.53</v>
+        <v>0.66</v>
       </c>
       <c r="J24">
-        <v>0.66</v>
-      </c>
-      <c r="K24" s="1">
         <v>13.74</v>
       </c>
-      <c r="L24" t="s">
-        <v>51</v>
+      <c r="K24" t="s">
+        <v>50</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
       </c>
       <c r="M24">
-        <v>0</v>
-      </c>
-      <c r="N24" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
+        <v>118615</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" s="3">
         <v>46199</v>
       </c>
       <c r="B25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D25" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F25">
-        <v>21.58</v>
-      </c>
-      <c r="G25" t="s">
-        <v>31</v>
+        <v>18.48</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0.65</v>
       </c>
       <c r="H25">
-        <v>0.65</v>
+        <v>12.01</v>
       </c>
       <c r="I25" s="1">
-        <v>14.03</v>
+        <v>0.66</v>
       </c>
       <c r="J25">
-        <v>0.66</v>
-      </c>
-      <c r="K25" s="1">
-        <v>14.24</v>
-      </c>
-      <c r="L25" t="s">
-        <v>52</v>
+        <v>12.2</v>
+      </c>
+      <c r="K25" t="s">
+        <v>51</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
       </c>
       <c r="M25">
-        <v>0</v>
-      </c>
-      <c r="N25" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
+        <v>119077</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" s="3">
         <v>46199</v>
       </c>
       <c r="B26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C26" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F26">
-        <v>18.48</v>
-      </c>
-      <c r="G26" t="s">
-        <v>31</v>
+        <v>21.58</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0.65</v>
       </c>
       <c r="H26">
-        <v>0.65</v>
+        <v>14.03</v>
       </c>
       <c r="I26" s="1">
-        <v>12.01</v>
+        <v>0.66</v>
       </c>
       <c r="J26">
-        <v>0.66</v>
-      </c>
-      <c r="K26" s="1">
-        <v>12.2</v>
-      </c>
-      <c r="L26" t="s">
-        <v>53</v>
+        <v>14.24</v>
+      </c>
+      <c r="K26" t="s">
+        <v>52</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
       </c>
       <c r="M26">
-        <v>0</v>
-      </c>
-      <c r="N26" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
+        <v>224670</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" s="3">
         <v>46200</v>
       </c>
       <c r="B27" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C27" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F27">
-        <v>30.41</v>
-      </c>
-      <c r="G27" t="s">
-        <v>31</v>
+        <v>22.23</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0.65</v>
       </c>
       <c r="H27">
-        <v>0.65</v>
+        <v>14.45</v>
       </c>
       <c r="I27" s="1">
-        <v>19.77</v>
+        <v>0.66</v>
       </c>
       <c r="J27">
-        <v>0.66</v>
-      </c>
-      <c r="K27" s="1">
-        <v>20.07</v>
-      </c>
-      <c r="L27" t="s">
-        <v>54</v>
+        <v>14.67</v>
+      </c>
+      <c r="K27" t="s">
+        <v>53</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
       </c>
       <c r="M27">
-        <v>210845</v>
-      </c>
-      <c r="N27" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
+        <v>119707</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" s="3">
         <v>46200</v>
       </c>
       <c r="B28" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F28">
-        <v>22.23</v>
-      </c>
-      <c r="G28" t="s">
-        <v>31</v>
+        <v>30.41</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0.65</v>
       </c>
       <c r="H28">
-        <v>0.65</v>
+        <v>19.77</v>
       </c>
       <c r="I28" s="1">
-        <v>14.45</v>
+        <v>0.66</v>
       </c>
       <c r="J28">
-        <v>0.66</v>
-      </c>
-      <c r="K28" s="1">
-        <v>14.67</v>
-      </c>
-      <c r="L28" t="s">
-        <v>55</v>
+        <v>20.07</v>
+      </c>
+      <c r="K28" t="s">
+        <v>54</v>
+      </c>
+      <c r="L28">
+        <v>210845</v>
       </c>
       <c r="M28">
-        <v>0</v>
-      </c>
-      <c r="N28" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
+        <v>119748</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" s="3">
         <v>46201</v>
       </c>
       <c r="B29" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C29" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" t="s">
         <v>23</v>
       </c>
-      <c r="D29" t="s">
-        <v>29</v>
-      </c>
       <c r="E29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F29">
-        <v>23.11</v>
-      </c>
-      <c r="G29" t="s">
-        <v>31</v>
+        <v>23.7</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0.65</v>
       </c>
       <c r="H29">
-        <v>0.65</v>
+        <v>15.4</v>
       </c>
       <c r="I29" s="1">
-        <v>15.02</v>
+        <v>0.66</v>
       </c>
       <c r="J29">
-        <v>0.66</v>
-      </c>
-      <c r="K29" s="1">
-        <v>15.25</v>
-      </c>
-      <c r="L29" t="s">
-        <v>56</v>
+        <v>15.64</v>
+      </c>
+      <c r="K29" t="s">
+        <v>55</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
       </c>
       <c r="M29">
-        <v>196489</v>
-      </c>
-      <c r="N29" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
+        <v>121687</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" s="3">
         <v>46201</v>
       </c>
       <c r="B30" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C30" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D30" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F30">
-        <v>21.32</v>
-      </c>
-      <c r="G30" t="s">
-        <v>31</v>
+        <v>23.11</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0.65</v>
       </c>
       <c r="H30">
-        <v>0.65</v>
+        <v>15.02</v>
       </c>
       <c r="I30" s="1">
-        <v>13.86</v>
+        <v>0.66</v>
       </c>
       <c r="J30">
-        <v>0.66</v>
-      </c>
-      <c r="K30" s="1">
-        <v>14.07</v>
-      </c>
-      <c r="L30" t="s">
-        <v>57</v>
+        <v>15.25</v>
+      </c>
+      <c r="K30" t="s">
+        <v>56</v>
+      </c>
+      <c r="L30">
+        <v>196489</v>
       </c>
       <c r="M30">
-        <v>189359</v>
-      </c>
-      <c r="N30" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
+        <v>120442</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="3">
         <v>46201</v>
       </c>
       <c r="B31" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F31">
-        <v>23.7</v>
-      </c>
-      <c r="G31" t="s">
-        <v>31</v>
+        <v>21.32</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0.65</v>
       </c>
       <c r="H31">
-        <v>0.65</v>
+        <v>13.86</v>
       </c>
       <c r="I31" s="1">
-        <v>15.4</v>
+        <v>0.66</v>
       </c>
       <c r="J31">
-        <v>0.66</v>
-      </c>
-      <c r="K31" s="1">
-        <v>15.64</v>
-      </c>
-      <c r="L31" t="s">
-        <v>58</v>
+        <v>14.07</v>
+      </c>
+      <c r="K31" t="s">
+        <v>57</v>
+      </c>
+      <c r="L31">
+        <v>189359</v>
       </c>
       <c r="M31">
-        <v>0</v>
-      </c>
-      <c r="N31" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
+        <v>120687</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" s="3">
         <v>46202</v>
       </c>
       <c r="B32" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F32">
         <v>23.11</v>
       </c>
-      <c r="G32" t="s">
-        <v>31</v>
+      <c r="G32" s="1">
+        <v>0.65</v>
       </c>
       <c r="H32">
-        <v>0.65</v>
+        <v>15.02</v>
       </c>
       <c r="I32" s="1">
-        <v>15.02</v>
+        <v>0.66</v>
       </c>
       <c r="J32">
-        <v>0.66</v>
-      </c>
-      <c r="K32" s="1">
         <v>15.25</v>
       </c>
-      <c r="L32" t="s">
-        <v>59</v>
+      <c r="K32" t="s">
+        <v>58</v>
+      </c>
+      <c r="L32">
+        <v>178788</v>
       </c>
       <c r="M32">
-        <v>178788</v>
-      </c>
-      <c r="N32" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14">
+        <v>120789</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33" s="3">
         <v>46202</v>
       </c>
       <c r="B33" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D33" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F33">
         <v>30.73</v>
       </c>
-      <c r="G33" t="s">
-        <v>31</v>
+      <c r="G33" s="1">
+        <v>0.65</v>
       </c>
       <c r="H33">
-        <v>0.65</v>
+        <v>19.97</v>
       </c>
       <c r="I33" s="1">
-        <v>19.97</v>
+        <v>0.66</v>
       </c>
       <c r="J33">
-        <v>0.66</v>
-      </c>
-      <c r="K33" s="1">
         <v>20.28</v>
       </c>
-      <c r="L33" t="s">
-        <v>60</v>
+      <c r="K33" t="s">
+        <v>59</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
       </c>
       <c r="M33">
-        <v>0</v>
-      </c>
-      <c r="N33" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14">
+        <v>120897</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" s="3">
         <v>46202</v>
       </c>
       <c r="B34" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D34" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F34">
         <v>28.27</v>
       </c>
-      <c r="G34" t="s">
-        <v>31</v>
+      <c r="G34" s="1">
+        <v>0.65</v>
       </c>
       <c r="H34">
-        <v>0.65</v>
+        <v>18.38</v>
       </c>
       <c r="I34" s="1">
-        <v>18.38</v>
+        <v>0.66</v>
       </c>
       <c r="J34">
-        <v>0.66</v>
-      </c>
-      <c r="K34" s="1">
         <v>18.66</v>
       </c>
-      <c r="L34" t="s">
-        <v>61</v>
+      <c r="K34" t="s">
+        <v>60</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
       </c>
       <c r="M34">
-        <v>0</v>
-      </c>
-      <c r="N34" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14">
+        <v>121222</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35" s="3">
         <v>46203</v>
       </c>
@@ -2253,89 +2042,83 @@
         <v>14</v>
       </c>
       <c r="C35" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D35" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F35">
         <v>21.56</v>
       </c>
-      <c r="G35" t="s">
-        <v>31</v>
+      <c r="G35" s="1">
+        <v>0.65</v>
       </c>
       <c r="H35">
-        <v>0.65</v>
+        <v>14.01</v>
       </c>
       <c r="I35" s="1">
-        <v>14.01</v>
+        <v>0.66</v>
       </c>
       <c r="J35">
-        <v>0.66</v>
-      </c>
-      <c r="K35" s="1">
         <v>14.23</v>
       </c>
-      <c r="L35" t="s">
-        <v>62</v>
+      <c r="K35" t="s">
+        <v>61</v>
+      </c>
+      <c r="L35">
+        <v>189496</v>
       </c>
       <c r="M35">
-        <v>189496</v>
-      </c>
-      <c r="N35" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14">
+        <v>226081</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" s="3">
         <v>46203</v>
       </c>
       <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="s">
         <v>17</v>
       </c>
-      <c r="C36" t="s">
-        <v>20</v>
-      </c>
       <c r="D36" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E36" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F36">
         <v>27.73</v>
       </c>
-      <c r="G36" t="s">
-        <v>31</v>
+      <c r="G36" s="1">
+        <v>0.65</v>
       </c>
       <c r="H36">
-        <v>0.65</v>
+        <v>18.02</v>
       </c>
       <c r="I36" s="1">
-        <v>18.02</v>
+        <v>0.66</v>
       </c>
       <c r="J36">
-        <v>0.66</v>
-      </c>
-      <c r="K36" s="1">
         <v>18.3</v>
       </c>
-      <c r="L36" t="s">
+      <c r="K36" t="s">
+        <v>62</v>
+      </c>
+      <c r="L36">
+        <v>211231</v>
+      </c>
+      <c r="M36">
+        <v>207127</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
+      <c r="A39" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="M36">
-        <v>211231</v>
-      </c>
-      <c r="N36" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14">
-      <c r="A39" s="4" t="s">
-        <v>99</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -2343,29 +2126,29 @@
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
     </row>
-    <row r="40" spans="1:14">
+    <row r="40" spans="1:13">
       <c r="A40" s="5" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>103</v>
+        <v>67</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
       <c r="A41" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B41" s="7">
         <v>866.5</v>
@@ -2383,9 +2166,9 @@
         <v>574.11</v>
       </c>
     </row>
-    <row r="42" spans="1:14">
+    <row r="42" spans="1:13">
       <c r="A42" s="9" t="s">
-        <v>104</v>
+        <v>68</v>
       </c>
       <c r="B42" s="10">
         <v>866.5</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ/ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ/ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ.xlsx
@@ -461,7 +461,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -3289,7 +3289,7 @@
         <v>44</v>
       </c>
       <c r="D59" s="8">
-        <v>0.6291</v>
+        <v>0.629105</v>
       </c>
       <c r="E59" s="7">
         <v>661.02</v>
@@ -3309,7 +3309,7 @@
         <v>6</v>
       </c>
       <c r="D60" s="8">
-        <v>1.756</v>
+        <v>1.756012</v>
       </c>
       <c r="E60" s="7">
         <v>170.14</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ/ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ/ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="147">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -853,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N62"/>
+  <dimension ref="A1:O62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -866,13 +869,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -915,2342 +918,2504 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F2">
         <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H2">
+        <v>1.369</v>
+      </c>
+      <c r="I2" s="1">
         <v>1.47</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>14.7</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>1.5</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L2" s="1">
         <v>15</v>
       </c>
-      <c r="L2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M2">
+      <c r="M2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N2">
         <v>197441</v>
       </c>
-      <c r="N2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="3">
         <v>46219</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F3">
-        <v>18.36</v>
+        <v>18.365</v>
       </c>
       <c r="G3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1">
         <v>0.62</v>
       </c>
-      <c r="I3" s="1">
-        <v>11.38</v>
-      </c>
       <c r="J3">
-        <v>0.63</v>
+        <v>11.3863</v>
       </c>
       <c r="K3" s="1">
-        <v>11.57</v>
-      </c>
-      <c r="L3" t="s">
-        <v>38</v>
-      </c>
-      <c r="M3">
+        <v>0.63</v>
+      </c>
+      <c r="L3" s="1">
+        <v>11.56995</v>
+      </c>
+      <c r="M3" t="s">
+        <v>39</v>
+      </c>
+      <c r="N3">
         <v>197441</v>
       </c>
-      <c r="N3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="3">
         <v>46219</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F4">
-        <v>34.09</v>
+        <v>34.095</v>
       </c>
       <c r="G4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1">
         <v>0.62</v>
       </c>
-      <c r="I4" s="1">
-        <v>21.14</v>
-      </c>
       <c r="J4">
-        <v>0.63</v>
+        <v>21.1389</v>
       </c>
       <c r="K4" s="1">
-        <v>21.48</v>
-      </c>
-      <c r="L4" t="s">
-        <v>39</v>
-      </c>
-      <c r="M4">
+        <v>0.63</v>
+      </c>
+      <c r="L4" s="1">
+        <v>21.47985</v>
+      </c>
+      <c r="M4" t="s">
+        <v>40</v>
+      </c>
+      <c r="N4">
         <v>0</v>
       </c>
-      <c r="N4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="3">
         <v>46219</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F5">
         <v>16.71</v>
       </c>
       <c r="G5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H5">
+        <v>1.629</v>
+      </c>
+      <c r="I5" s="1">
         <v>1.72</v>
       </c>
-      <c r="I5" s="1">
-        <v>28.74</v>
-      </c>
       <c r="J5">
+        <v>28.7412</v>
+      </c>
+      <c r="K5" s="1">
         <v>1.76</v>
       </c>
-      <c r="K5" s="1">
-        <v>29.41</v>
-      </c>
-      <c r="L5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M5">
+      <c r="L5" s="1">
+        <v>29.4096</v>
+      </c>
+      <c r="M5" t="s">
+        <v>41</v>
+      </c>
+      <c r="N5">
         <v>72365</v>
       </c>
-      <c r="N5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="3">
         <v>46219</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F6">
-        <v>17.22</v>
+        <v>17.222</v>
       </c>
       <c r="G6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H6">
+        <v>1.629</v>
+      </c>
+      <c r="I6" s="1">
         <v>1.72</v>
       </c>
-      <c r="I6" s="1">
-        <v>29.62</v>
-      </c>
       <c r="J6">
+        <v>29.62184</v>
+      </c>
+      <c r="K6" s="1">
         <v>1.76</v>
       </c>
-      <c r="K6" s="1">
-        <v>30.31</v>
-      </c>
-      <c r="L6" t="s">
-        <v>41</v>
-      </c>
-      <c r="M6">
+      <c r="L6" s="1">
+        <v>30.31072</v>
+      </c>
+      <c r="M6" t="s">
+        <v>42</v>
+      </c>
+      <c r="N6">
         <v>0</v>
       </c>
-      <c r="N6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="3">
         <v>46219</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F7">
-        <v>24.14</v>
+        <v>24.143</v>
       </c>
       <c r="G7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
         <v>0.62</v>
       </c>
-      <c r="I7" s="1">
-        <v>14.97</v>
-      </c>
       <c r="J7">
-        <v>0.63</v>
+        <v>14.96866</v>
       </c>
       <c r="K7" s="1">
-        <v>15.21</v>
-      </c>
-      <c r="L7" t="s">
-        <v>42</v>
-      </c>
-      <c r="M7">
+        <v>0.63</v>
+      </c>
+      <c r="L7" s="1">
+        <v>15.21009</v>
+      </c>
+      <c r="M7" t="s">
+        <v>43</v>
+      </c>
+      <c r="N7">
         <v>212759</v>
       </c>
-      <c r="N7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="3">
         <v>46219</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F8">
-        <v>17.49</v>
+        <v>17.492</v>
       </c>
       <c r="G8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1">
         <v>0.62</v>
       </c>
-      <c r="I8" s="1">
-        <v>10.84</v>
-      </c>
       <c r="J8">
-        <v>0.63</v>
+        <v>10.84504</v>
       </c>
       <c r="K8" s="1">
-        <v>11.02</v>
-      </c>
-      <c r="L8" t="s">
-        <v>43</v>
-      </c>
-      <c r="M8">
+        <v>0.63</v>
+      </c>
+      <c r="L8" s="1">
+        <v>11.01996</v>
+      </c>
+      <c r="M8" t="s">
+        <v>44</v>
+      </c>
+      <c r="N8">
         <v>0</v>
       </c>
-      <c r="N8" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="3">
         <v>46220</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F9">
-        <v>21.31</v>
+        <v>21.313</v>
       </c>
       <c r="G9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H9">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I9" s="1">
-        <v>13.43</v>
+        <v>0.63</v>
       </c>
       <c r="J9">
-        <v>0.64</v>
+        <v>13.42719</v>
       </c>
       <c r="K9" s="1">
-        <v>13.64</v>
-      </c>
-      <c r="L9" t="s">
-        <v>44</v>
-      </c>
-      <c r="M9">
+        <v>0.64</v>
+      </c>
+      <c r="L9" s="1">
+        <v>13.64032</v>
+      </c>
+      <c r="M9" t="s">
+        <v>45</v>
+      </c>
+      <c r="N9">
         <v>0</v>
       </c>
-      <c r="N9" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="3">
         <v>46220</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F10">
-        <v>23.94</v>
+        <v>23.938</v>
       </c>
       <c r="G10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H10">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I10" s="1">
-        <v>15.08</v>
+        <v>0.63</v>
       </c>
       <c r="J10">
-        <v>0.64</v>
+        <v>15.08094</v>
       </c>
       <c r="K10" s="1">
-        <v>15.32</v>
-      </c>
-      <c r="L10" t="s">
-        <v>45</v>
-      </c>
-      <c r="M10">
+        <v>0.64</v>
+      </c>
+      <c r="L10" s="1">
+        <v>15.32032</v>
+      </c>
+      <c r="M10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N10">
         <v>0</v>
       </c>
-      <c r="N10" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="O10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="3">
         <v>46220</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F11">
-        <v>20.23</v>
+        <v>20.234</v>
       </c>
       <c r="G11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H11">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I11" s="1">
-        <v>12.74</v>
+        <v>0.63</v>
       </c>
       <c r="J11">
-        <v>0.64</v>
+        <v>12.74742</v>
       </c>
       <c r="K11" s="1">
-        <v>12.95</v>
-      </c>
-      <c r="L11" t="s">
-        <v>46</v>
-      </c>
-      <c r="M11">
+        <v>0.64</v>
+      </c>
+      <c r="L11" s="1">
+        <v>12.94976</v>
+      </c>
+      <c r="M11" t="s">
+        <v>47</v>
+      </c>
+      <c r="N11">
         <v>190762</v>
       </c>
-      <c r="N11" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="O11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="3">
         <v>46221</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F12">
-        <v>21.27</v>
+        <v>21.266</v>
       </c>
       <c r="G12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H12">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I12" s="1">
-        <v>13.4</v>
+        <v>0.63</v>
       </c>
       <c r="J12">
-        <v>0.64</v>
+        <v>13.39758</v>
       </c>
       <c r="K12" s="1">
-        <v>13.61</v>
-      </c>
-      <c r="L12" t="s">
-        <v>47</v>
-      </c>
-      <c r="M12">
+        <v>0.64</v>
+      </c>
+      <c r="L12" s="1">
+        <v>13.61024</v>
+      </c>
+      <c r="M12" t="s">
+        <v>48</v>
+      </c>
+      <c r="N12">
         <v>197554</v>
       </c>
-      <c r="N12" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O12" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="3">
         <v>46221</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13">
-        <v>21.77</v>
+        <v>21.766</v>
       </c>
       <c r="G13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H13">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I13" s="1">
-        <v>13.72</v>
+        <v>0.63</v>
       </c>
       <c r="J13">
-        <v>0.64</v>
+        <v>13.71258</v>
       </c>
       <c r="K13" s="1">
-        <v>13.93</v>
-      </c>
-      <c r="L13" t="s">
-        <v>48</v>
-      </c>
-      <c r="M13">
+        <v>0.64</v>
+      </c>
+      <c r="L13" s="1">
+        <v>13.93024</v>
+      </c>
+      <c r="M13" t="s">
+        <v>49</v>
+      </c>
+      <c r="N13">
         <v>212998</v>
       </c>
-      <c r="N13" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="O13" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" s="3">
         <v>46221</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F14">
-        <v>20.67</v>
+        <v>20.672</v>
       </c>
       <c r="G14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H14">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I14" s="1">
-        <v>13.02</v>
+        <v>0.63</v>
       </c>
       <c r="J14">
-        <v>0.64</v>
+        <v>13.02336</v>
       </c>
       <c r="K14" s="1">
-        <v>13.23</v>
-      </c>
-      <c r="L14" t="s">
-        <v>48</v>
-      </c>
-      <c r="M14">
+        <v>0.64</v>
+      </c>
+      <c r="L14" s="1">
+        <v>13.23008</v>
+      </c>
+      <c r="M14" t="s">
+        <v>49</v>
+      </c>
+      <c r="N14">
         <v>0</v>
       </c>
-      <c r="N14" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="O14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" s="3">
         <v>46222</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F15">
-        <v>15.02</v>
+        <v>15.016</v>
       </c>
       <c r="G15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H15">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I15" s="1">
-        <v>9.460000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="J15">
-        <v>0.64</v>
+        <v>9.46008</v>
       </c>
       <c r="K15" s="1">
-        <v>9.609999999999999</v>
-      </c>
-      <c r="L15" t="s">
-        <v>49</v>
-      </c>
-      <c r="M15">
+        <v>0.64</v>
+      </c>
+      <c r="L15" s="1">
+        <v>9.610239999999999</v>
+      </c>
+      <c r="M15" t="s">
+        <v>50</v>
+      </c>
+      <c r="N15">
         <v>0</v>
       </c>
-      <c r="N15" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="O15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" s="3">
         <v>46222</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F16">
-        <v>22.34</v>
+        <v>22.344</v>
       </c>
       <c r="G16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H16">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I16" s="1">
-        <v>14.07</v>
+        <v>0.63</v>
       </c>
       <c r="J16">
-        <v>0.64</v>
+        <v>14.07672</v>
       </c>
       <c r="K16" s="1">
-        <v>14.3</v>
-      </c>
-      <c r="L16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M16">
+        <v>0.64</v>
+      </c>
+      <c r="L16" s="1">
+        <v>14.30016</v>
+      </c>
+      <c r="M16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16">
         <v>0</v>
       </c>
-      <c r="N16" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="O16" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17" s="3">
         <v>46223</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F17">
-        <v>31.95</v>
+        <v>31.953</v>
       </c>
       <c r="G17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H17">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I17" s="1">
-        <v>20.13</v>
+        <v>0.63</v>
       </c>
       <c r="J17">
-        <v>0.64</v>
+        <v>20.13039</v>
       </c>
       <c r="K17" s="1">
-        <v>20.45</v>
-      </c>
-      <c r="L17" t="s">
-        <v>51</v>
-      </c>
-      <c r="M17">
+        <v>0.64</v>
+      </c>
+      <c r="L17" s="1">
+        <v>20.44992</v>
+      </c>
+      <c r="M17" t="s">
+        <v>52</v>
+      </c>
+      <c r="N17">
         <v>0</v>
       </c>
-      <c r="N17" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="O17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18" s="3">
         <v>46223</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F18">
-        <v>30.47</v>
+        <v>30.469</v>
       </c>
       <c r="G18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H18">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I18" s="1">
-        <v>19.2</v>
+        <v>0.63</v>
       </c>
       <c r="J18">
-        <v>0.64</v>
+        <v>19.19547</v>
       </c>
       <c r="K18" s="1">
-        <v>19.5</v>
-      </c>
-      <c r="L18" t="s">
-        <v>52</v>
-      </c>
-      <c r="M18">
+        <v>0.64</v>
+      </c>
+      <c r="L18" s="1">
+        <v>19.50016</v>
+      </c>
+      <c r="M18" t="s">
+        <v>53</v>
+      </c>
+      <c r="N18">
         <v>213276</v>
       </c>
-      <c r="N18" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="O18" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" s="3">
         <v>46223</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F19">
-        <v>22.31</v>
+        <v>22.313</v>
       </c>
       <c r="G19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H19">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I19" s="1">
-        <v>14.06</v>
+        <v>0.63</v>
       </c>
       <c r="J19">
-        <v>0.64</v>
+        <v>14.05719</v>
       </c>
       <c r="K19" s="1">
-        <v>14.28</v>
-      </c>
-      <c r="L19" t="s">
-        <v>53</v>
-      </c>
-      <c r="M19">
+        <v>0.64</v>
+      </c>
+      <c r="L19" s="1">
+        <v>14.28032</v>
+      </c>
+      <c r="M19" t="s">
+        <v>54</v>
+      </c>
+      <c r="N19">
         <v>197721</v>
       </c>
-      <c r="N19" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="O19" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20" s="3">
         <v>46223</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F20">
-        <v>15.34</v>
+        <v>15.344</v>
       </c>
       <c r="G20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H20">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I20" s="1">
-        <v>9.66</v>
+        <v>0.63</v>
       </c>
       <c r="J20">
-        <v>0.64</v>
+        <v>9.66672</v>
       </c>
       <c r="K20" s="1">
-        <v>9.82</v>
-      </c>
-      <c r="L20" t="s">
-        <v>54</v>
-      </c>
-      <c r="M20">
+        <v>0.64</v>
+      </c>
+      <c r="L20" s="1">
+        <v>9.82016</v>
+      </c>
+      <c r="M20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N20">
         <v>179669</v>
       </c>
-      <c r="N20" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="O20" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" s="3">
         <v>46224</v>
       </c>
       <c r="B21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F21">
-        <v>28.36</v>
+        <v>28.359</v>
       </c>
       <c r="G21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H21">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I21" s="1">
-        <v>17.87</v>
+        <v>0.63</v>
       </c>
       <c r="J21">
-        <v>0.64</v>
+        <v>17.86617</v>
       </c>
       <c r="K21" s="1">
-        <v>18.15</v>
-      </c>
-      <c r="L21" t="s">
-        <v>55</v>
-      </c>
-      <c r="M21">
+        <v>0.64</v>
+      </c>
+      <c r="L21" s="1">
+        <v>18.14976</v>
+      </c>
+      <c r="M21" t="s">
+        <v>56</v>
+      </c>
+      <c r="N21">
         <v>155523</v>
       </c>
-      <c r="N21" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="O21" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" s="3">
         <v>46224</v>
       </c>
       <c r="B22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E22" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F22">
         <v>28.5</v>
       </c>
       <c r="G22" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H22">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I22" s="1">
-        <v>17.96</v>
+        <v>0.63</v>
       </c>
       <c r="J22">
-        <v>0.64</v>
+        <v>17.955</v>
       </c>
       <c r="K22" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="L22" s="1">
         <v>18.24</v>
       </c>
-      <c r="L22" t="s">
-        <v>56</v>
-      </c>
-      <c r="M22">
+      <c r="M22" t="s">
+        <v>57</v>
+      </c>
+      <c r="N22">
         <v>0</v>
       </c>
-      <c r="N22" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="O22" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
       <c r="A23" s="3">
         <v>46225</v>
       </c>
       <c r="B23" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F23">
-        <v>32.11</v>
+        <v>32.109</v>
       </c>
       <c r="G23" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H23">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I23" s="1">
-        <v>20.23</v>
+        <v>0.63</v>
       </c>
       <c r="J23">
-        <v>0.64</v>
+        <v>20.22867</v>
       </c>
       <c r="K23" s="1">
-        <v>20.55</v>
-      </c>
-      <c r="L23" t="s">
-        <v>57</v>
-      </c>
-      <c r="M23">
+        <v>0.64</v>
+      </c>
+      <c r="L23" s="1">
+        <v>20.54976</v>
+      </c>
+      <c r="M23" t="s">
+        <v>58</v>
+      </c>
+      <c r="N23">
         <v>0</v>
       </c>
-      <c r="N23" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
+      <c r="O23" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24" s="3">
         <v>46225</v>
       </c>
       <c r="B24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E24" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F24">
-        <v>23.8</v>
+        <v>23.797</v>
       </c>
       <c r="G24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H24">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I24" s="1">
-        <v>14.99</v>
+        <v>0.63</v>
       </c>
       <c r="J24">
-        <v>0.64</v>
+        <v>14.99211</v>
       </c>
       <c r="K24" s="1">
-        <v>15.23</v>
-      </c>
-      <c r="L24" t="s">
-        <v>58</v>
-      </c>
-      <c r="M24">
+        <v>0.64</v>
+      </c>
+      <c r="L24" s="1">
+        <v>15.23008</v>
+      </c>
+      <c r="M24" t="s">
+        <v>59</v>
+      </c>
+      <c r="N24">
         <v>0</v>
       </c>
-      <c r="N24" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
+      <c r="O24" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
       <c r="A25" s="3">
         <v>46225</v>
       </c>
       <c r="B25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E25" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F25">
         <v>5</v>
       </c>
       <c r="G25" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H25">
+        <v>1.401</v>
+      </c>
+      <c r="I25" s="1">
         <v>1.51</v>
       </c>
-      <c r="I25" s="1">
+      <c r="J25">
         <v>7.55</v>
       </c>
-      <c r="J25">
+      <c r="K25" s="1">
         <v>1.54</v>
       </c>
-      <c r="K25" s="1">
+      <c r="L25" s="1">
         <v>7.7</v>
       </c>
-      <c r="L25" t="s">
-        <v>59</v>
-      </c>
-      <c r="M25">
+      <c r="M25" t="s">
+        <v>60</v>
+      </c>
+      <c r="N25">
         <v>0</v>
       </c>
-      <c r="N25" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
+      <c r="O25" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
       <c r="A26" s="3">
         <v>46226</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C26" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E26" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F26">
-        <v>23.33</v>
+        <v>23.328</v>
       </c>
       <c r="G26" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H26">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I26" s="1">
-        <v>14.7</v>
+        <v>0.63</v>
       </c>
       <c r="J26">
-        <v>0.64</v>
+        <v>14.69664</v>
       </c>
       <c r="K26" s="1">
-        <v>14.93</v>
-      </c>
-      <c r="L26" t="s">
-        <v>60</v>
-      </c>
-      <c r="M26">
+        <v>0.64</v>
+      </c>
+      <c r="L26" s="1">
+        <v>14.92992</v>
+      </c>
+      <c r="M26" t="s">
+        <v>61</v>
+      </c>
+      <c r="N26">
         <v>197837</v>
       </c>
-      <c r="N26" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
+      <c r="O26" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
       <c r="A27" s="3">
         <v>46226</v>
       </c>
       <c r="B27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F27">
-        <v>20.2</v>
+        <v>20.203</v>
       </c>
       <c r="G27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H27">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I27" s="1">
-        <v>12.73</v>
+        <v>0.63</v>
       </c>
       <c r="J27">
-        <v>0.64</v>
+        <v>12.72789</v>
       </c>
       <c r="K27" s="1">
-        <v>12.93</v>
-      </c>
-      <c r="L27" t="s">
-        <v>61</v>
-      </c>
-      <c r="M27">
+        <v>0.64</v>
+      </c>
+      <c r="L27" s="1">
+        <v>12.92992</v>
+      </c>
+      <c r="M27" t="s">
+        <v>62</v>
+      </c>
+      <c r="N27">
         <v>179911</v>
       </c>
-      <c r="N27" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
+      <c r="O27" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
       <c r="A28" s="3">
         <v>46227</v>
       </c>
       <c r="B28" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D28" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F28">
-        <v>20.56</v>
+        <v>20.563</v>
       </c>
       <c r="G28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H28">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I28" s="1">
-        <v>12.95</v>
+        <v>0.63</v>
       </c>
       <c r="J28">
-        <v>0.64</v>
+        <v>12.95469</v>
       </c>
       <c r="K28" s="1">
-        <v>13.16</v>
-      </c>
-      <c r="L28" t="s">
-        <v>62</v>
-      </c>
-      <c r="M28">
+        <v>0.64</v>
+      </c>
+      <c r="L28" s="1">
+        <v>13.16032</v>
+      </c>
+      <c r="M28" t="s">
+        <v>63</v>
+      </c>
+      <c r="N28">
         <v>0</v>
       </c>
-      <c r="N28" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
+      <c r="O28" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
       <c r="A29" s="3">
         <v>46227</v>
       </c>
       <c r="B29" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F29">
-        <v>26.91</v>
+        <v>26.906</v>
       </c>
       <c r="G29" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H29">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I29" s="1">
-        <v>16.95</v>
+        <v>0.63</v>
       </c>
       <c r="J29">
-        <v>0.64</v>
+        <v>16.95078</v>
       </c>
       <c r="K29" s="1">
-        <v>17.22</v>
-      </c>
-      <c r="L29" t="s">
-        <v>63</v>
-      </c>
-      <c r="M29">
+        <v>0.64</v>
+      </c>
+      <c r="L29" s="1">
+        <v>17.21984</v>
+      </c>
+      <c r="M29" t="s">
+        <v>64</v>
+      </c>
+      <c r="N29">
         <v>0</v>
       </c>
-      <c r="N29" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
+      <c r="O29" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
       <c r="A30" s="3">
         <v>46228</v>
       </c>
       <c r="B30" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E30" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F30">
-        <v>26.62</v>
+        <v>26.625</v>
       </c>
       <c r="G30" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H30">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I30" s="1">
-        <v>16.77</v>
+        <v>0.63</v>
       </c>
       <c r="J30">
-        <v>0.64</v>
+        <v>16.77375</v>
       </c>
       <c r="K30" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="L30" s="1">
         <v>17.04</v>
       </c>
-      <c r="L30" t="s">
-        <v>64</v>
-      </c>
-      <c r="M30">
+      <c r="M30" t="s">
+        <v>65</v>
+      </c>
+      <c r="N30">
         <v>180198</v>
       </c>
-      <c r="N30" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
+      <c r="O30" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
       <c r="A31" s="3">
         <v>46228</v>
       </c>
       <c r="B31" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D31" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E31" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F31">
         <v>16</v>
       </c>
       <c r="G31" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H31">
+        <v>1.649</v>
+      </c>
+      <c r="I31" s="1">
         <v>1.77</v>
       </c>
-      <c r="I31" s="1">
+      <c r="J31">
         <v>28.32</v>
       </c>
-      <c r="J31">
+      <c r="K31" s="1">
         <v>1.81</v>
       </c>
-      <c r="K31" s="1">
+      <c r="L31" s="1">
         <v>28.96</v>
       </c>
-      <c r="L31" t="s">
-        <v>65</v>
-      </c>
-      <c r="M31">
+      <c r="M31" t="s">
+        <v>66</v>
+      </c>
+      <c r="N31">
         <v>72540</v>
       </c>
-      <c r="N31" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
+      <c r="O31" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
       <c r="A32" s="3">
         <v>46228</v>
       </c>
       <c r="B32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E32" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F32">
         <v>13</v>
       </c>
       <c r="G32" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H32">
+        <v>1.649</v>
+      </c>
+      <c r="I32" s="1">
         <v>1.77</v>
       </c>
-      <c r="I32" s="1">
+      <c r="J32">
         <v>23.01</v>
       </c>
-      <c r="J32">
+      <c r="K32" s="1">
         <v>1.81</v>
       </c>
-      <c r="K32" s="1">
+      <c r="L32" s="1">
         <v>23.53</v>
       </c>
-      <c r="L32" t="s">
-        <v>65</v>
-      </c>
-      <c r="M32">
+      <c r="M32" t="s">
+        <v>66</v>
+      </c>
+      <c r="N32">
         <v>72840</v>
       </c>
-      <c r="N32" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14">
+      <c r="O32" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
       <c r="A33" s="3">
         <v>46228</v>
       </c>
       <c r="B33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D33" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F33">
-        <v>22.41</v>
+        <v>22.406</v>
       </c>
       <c r="G33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H33">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I33" s="1">
-        <v>14.12</v>
+        <v>0.63</v>
       </c>
       <c r="J33">
-        <v>0.64</v>
+        <v>14.11578</v>
       </c>
       <c r="K33" s="1">
-        <v>14.34</v>
-      </c>
-      <c r="L33" t="s">
-        <v>66</v>
-      </c>
-      <c r="M33">
+        <v>0.64</v>
+      </c>
+      <c r="L33" s="1">
+        <v>14.33984</v>
+      </c>
+      <c r="M33" t="s">
+        <v>67</v>
+      </c>
+      <c r="N33">
         <v>213871</v>
       </c>
-      <c r="N33" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14">
+      <c r="O33" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15">
       <c r="A34" s="3">
         <v>46229</v>
       </c>
       <c r="B34" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C34" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D34" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E34" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F34">
-        <v>21.81</v>
+        <v>21.813</v>
       </c>
       <c r="G34" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H34">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I34" s="1">
-        <v>13.74</v>
+        <v>0.63</v>
       </c>
       <c r="J34">
-        <v>0.64</v>
+        <v>13.74219</v>
       </c>
       <c r="K34" s="1">
-        <v>13.96</v>
-      </c>
-      <c r="L34" t="s">
-        <v>67</v>
-      </c>
-      <c r="M34">
+        <v>0.64</v>
+      </c>
+      <c r="L34" s="1">
+        <v>13.96032</v>
+      </c>
+      <c r="M34" t="s">
+        <v>68</v>
+      </c>
+      <c r="N34">
         <v>0</v>
       </c>
-      <c r="N34" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14">
+      <c r="O34" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15">
       <c r="A35" s="3">
         <v>46229</v>
       </c>
       <c r="B35" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D35" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E35" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F35">
-        <v>25.61</v>
+        <v>25.609</v>
       </c>
       <c r="G35" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H35">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I35" s="1">
-        <v>16.13</v>
+        <v>0.63</v>
       </c>
       <c r="J35">
-        <v>0.64</v>
+        <v>16.13367</v>
       </c>
       <c r="K35" s="1">
-        <v>16.39</v>
-      </c>
-      <c r="L35" t="s">
-        <v>68</v>
-      </c>
-      <c r="M35">
+        <v>0.64</v>
+      </c>
+      <c r="L35" s="1">
+        <v>16.38976</v>
+      </c>
+      <c r="M35" t="s">
+        <v>69</v>
+      </c>
+      <c r="N35">
         <v>0</v>
       </c>
-      <c r="N35" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14">
+      <c r="O35" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15">
       <c r="A36" s="3">
         <v>46229</v>
       </c>
       <c r="B36" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C36" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D36" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F36">
-        <v>21.88</v>
+        <v>21.875</v>
       </c>
       <c r="G36" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H36">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I36" s="1">
-        <v>13.78</v>
+        <v>0.63</v>
       </c>
       <c r="J36">
-        <v>0.64</v>
+        <v>13.78125</v>
       </c>
       <c r="K36" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="L36" s="1">
         <v>14</v>
       </c>
-      <c r="L36" t="s">
-        <v>69</v>
-      </c>
-      <c r="M36">
+      <c r="M36" t="s">
+        <v>70</v>
+      </c>
+      <c r="N36">
         <v>0</v>
       </c>
-      <c r="N36" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14">
+      <c r="O36" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15">
       <c r="A37" s="3">
         <v>46229</v>
       </c>
       <c r="B37" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C37" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D37" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E37" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F37">
-        <v>17.09</v>
+        <v>17.094</v>
       </c>
       <c r="G37" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H37">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I37" s="1">
-        <v>10.77</v>
+        <v>0.63</v>
       </c>
       <c r="J37">
-        <v>0.64</v>
+        <v>10.76922</v>
       </c>
       <c r="K37" s="1">
-        <v>10.94</v>
-      </c>
-      <c r="L37" t="s">
-        <v>70</v>
-      </c>
-      <c r="M37">
+        <v>0.64</v>
+      </c>
+      <c r="L37" s="1">
+        <v>10.94016</v>
+      </c>
+      <c r="M37" t="s">
+        <v>71</v>
+      </c>
+      <c r="N37">
         <v>197920</v>
       </c>
-      <c r="N37" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14">
+      <c r="O37" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15">
       <c r="A38" s="3">
         <v>46230</v>
       </c>
       <c r="B38" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C38" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D38" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F38">
-        <v>25.89</v>
+        <v>25.891</v>
       </c>
       <c r="G38" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H38">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I38" s="1">
-        <v>16.31</v>
+        <v>0.63</v>
       </c>
       <c r="J38">
-        <v>0.64</v>
+        <v>16.31133</v>
       </c>
       <c r="K38" s="1">
-        <v>16.57</v>
-      </c>
-      <c r="L38" t="s">
-        <v>71</v>
-      </c>
-      <c r="M38">
+        <v>0.64</v>
+      </c>
+      <c r="L38" s="1">
+        <v>16.57024</v>
+      </c>
+      <c r="M38" t="s">
+        <v>72</v>
+      </c>
+      <c r="N38">
         <v>0</v>
       </c>
-      <c r="N38" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14">
+      <c r="O38" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15">
       <c r="A39" s="3">
         <v>46230</v>
       </c>
       <c r="B39" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E39" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F39">
-        <v>25.77</v>
+        <v>25.766</v>
       </c>
       <c r="G39" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H39">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I39" s="1">
-        <v>16.24</v>
+        <v>0.63</v>
       </c>
       <c r="J39">
-        <v>0.64</v>
+        <v>16.23258</v>
       </c>
       <c r="K39" s="1">
-        <v>16.49</v>
-      </c>
-      <c r="L39" t="s">
-        <v>72</v>
-      </c>
-      <c r="M39">
+        <v>0.64</v>
+      </c>
+      <c r="L39" s="1">
+        <v>16.49024</v>
+      </c>
+      <c r="M39" t="s">
+        <v>73</v>
+      </c>
+      <c r="N39">
         <v>198059</v>
       </c>
-      <c r="N39" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14">
+      <c r="O39" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15">
       <c r="A40" s="3">
         <v>46231</v>
       </c>
       <c r="B40" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C40" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D40" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E40" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F40">
         <v>10</v>
       </c>
       <c r="G40" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H40">
+        <v>1.441</v>
+      </c>
+      <c r="I40" s="1">
         <v>1.53</v>
       </c>
-      <c r="I40" s="1">
+      <c r="J40">
         <v>15.3</v>
       </c>
-      <c r="J40">
+      <c r="K40" s="1">
         <v>1.56</v>
       </c>
-      <c r="K40" s="1">
+      <c r="L40" s="1">
         <v>15.6</v>
       </c>
-      <c r="L40" t="s">
-        <v>73</v>
-      </c>
-      <c r="M40">
+      <c r="M40" t="s">
+        <v>74</v>
+      </c>
+      <c r="N40">
         <v>0</v>
       </c>
-      <c r="N40" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14">
+      <c r="O40" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15">
       <c r="A41" s="3">
         <v>46231</v>
       </c>
       <c r="B41" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C41" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D41" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E41" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F41">
-        <v>36.45</v>
+        <v>36.453</v>
       </c>
       <c r="G41" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H41">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I41" s="1">
-        <v>22.96</v>
+        <v>0.63</v>
       </c>
       <c r="J41">
-        <v>0.64</v>
+        <v>22.96539</v>
       </c>
       <c r="K41" s="1">
-        <v>23.33</v>
-      </c>
-      <c r="L41" t="s">
-        <v>74</v>
-      </c>
-      <c r="M41">
+        <v>0.64</v>
+      </c>
+      <c r="L41" s="1">
+        <v>23.32992</v>
+      </c>
+      <c r="M41" t="s">
+        <v>75</v>
+      </c>
+      <c r="N41">
         <v>0</v>
       </c>
-      <c r="N41" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14">
+      <c r="O41" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15">
       <c r="A42" s="3">
         <v>46231</v>
       </c>
       <c r="B42" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C42" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D42" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E42" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F42">
-        <v>16.32</v>
+        <v>16.319</v>
       </c>
       <c r="G42" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H42">
+        <v>1.669</v>
+      </c>
+      <c r="I42" s="1">
         <v>1.78</v>
       </c>
-      <c r="I42" s="1">
-        <v>29.05</v>
-      </c>
       <c r="J42">
+        <v>29.04782</v>
+      </c>
+      <c r="K42" s="1">
         <v>1.82</v>
       </c>
-      <c r="K42" s="1">
-        <v>29.7</v>
-      </c>
-      <c r="L42" t="s">
-        <v>75</v>
-      </c>
-      <c r="M42">
+      <c r="L42" s="1">
+        <v>29.70058</v>
+      </c>
+      <c r="M42" t="s">
+        <v>76</v>
+      </c>
+      <c r="N42">
         <v>73026</v>
       </c>
-      <c r="N42" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14">
+      <c r="O42" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15">
       <c r="A43" s="3">
         <v>46231</v>
       </c>
       <c r="B43" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C43" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D43" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E43" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F43">
-        <v>27.77</v>
+        <v>27.766</v>
       </c>
       <c r="G43" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H43">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I43" s="1">
-        <v>17.5</v>
+        <v>0.63</v>
       </c>
       <c r="J43">
-        <v>0.64</v>
+        <v>17.49258</v>
       </c>
       <c r="K43" s="1">
-        <v>17.77</v>
-      </c>
-      <c r="L43" t="s">
-        <v>76</v>
-      </c>
-      <c r="M43">
+        <v>0.64</v>
+      </c>
+      <c r="L43" s="1">
+        <v>17.77024</v>
+      </c>
+      <c r="M43" t="s">
+        <v>77</v>
+      </c>
+      <c r="N43">
         <v>198198</v>
       </c>
-      <c r="N43" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14">
+      <c r="O43" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15">
       <c r="A44" s="3">
         <v>46231</v>
       </c>
       <c r="B44" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D44" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E44" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F44">
-        <v>17.64</v>
+        <v>17.637</v>
       </c>
       <c r="G44" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H44">
+        <v>1.669</v>
+      </c>
+      <c r="I44" s="1">
         <v>1.78</v>
       </c>
-      <c r="I44" s="1">
-        <v>31.4</v>
-      </c>
       <c r="J44">
+        <v>31.39386</v>
+      </c>
+      <c r="K44" s="1">
         <v>1.82</v>
       </c>
-      <c r="K44" s="1">
-        <v>32.1</v>
-      </c>
-      <c r="L44" t="s">
-        <v>77</v>
-      </c>
-      <c r="M44">
+      <c r="L44" s="1">
+        <v>32.09934</v>
+      </c>
+      <c r="M44" t="s">
+        <v>78</v>
+      </c>
+      <c r="N44">
         <v>0</v>
       </c>
-      <c r="N44" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14">
+      <c r="O44" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15">
       <c r="A45" s="3">
         <v>46231</v>
       </c>
       <c r="B45" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C45" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D45" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E45" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F45">
-        <v>23.05</v>
+        <v>23.047</v>
       </c>
       <c r="G45" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H45">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I45" s="1">
-        <v>14.52</v>
+        <v>0.63</v>
       </c>
       <c r="J45">
-        <v>0.64</v>
+        <v>14.51961</v>
       </c>
       <c r="K45" s="1">
-        <v>14.75</v>
-      </c>
-      <c r="L45" t="s">
-        <v>78</v>
-      </c>
-      <c r="M45">
+        <v>0.64</v>
+      </c>
+      <c r="L45" s="1">
+        <v>14.75008</v>
+      </c>
+      <c r="M45" t="s">
+        <v>79</v>
+      </c>
+      <c r="N45">
         <v>0</v>
       </c>
-      <c r="N45" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14">
+      <c r="O45" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15">
       <c r="A46" s="3">
         <v>46231</v>
       </c>
       <c r="B46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C46" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D46" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E46" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F46">
-        <v>24.66</v>
+        <v>24.656</v>
       </c>
       <c r="G46" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H46">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I46" s="1">
-        <v>15.54</v>
+        <v>0.63</v>
       </c>
       <c r="J46">
-        <v>0.64</v>
+        <v>15.53328</v>
       </c>
       <c r="K46" s="1">
-        <v>15.78</v>
-      </c>
-      <c r="L46" t="s">
-        <v>79</v>
-      </c>
-      <c r="M46">
+        <v>0.64</v>
+      </c>
+      <c r="L46" s="1">
+        <v>15.77984</v>
+      </c>
+      <c r="M46" t="s">
+        <v>80</v>
+      </c>
+      <c r="N46">
         <v>180491</v>
       </c>
-      <c r="N46" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14">
+      <c r="O46" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15">
       <c r="A47" s="3">
         <v>46232</v>
       </c>
       <c r="B47" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C47" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E47" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F47">
-        <v>20.27</v>
+        <v>20.266</v>
       </c>
       <c r="G47" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H47">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I47" s="1">
-        <v>12.77</v>
+        <v>0.63</v>
       </c>
       <c r="J47">
-        <v>0.64</v>
+        <v>12.76758</v>
       </c>
       <c r="K47" s="1">
-        <v>12.97</v>
-      </c>
-      <c r="L47" t="s">
-        <v>80</v>
-      </c>
-      <c r="M47">
+        <v>0.64</v>
+      </c>
+      <c r="L47" s="1">
+        <v>12.97024</v>
+      </c>
+      <c r="M47" t="s">
+        <v>81</v>
+      </c>
+      <c r="N47">
         <v>198312</v>
       </c>
-      <c r="N47" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14">
+      <c r="O47" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15">
       <c r="A48" s="3">
         <v>46232</v>
       </c>
       <c r="B48" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C48" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D48" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E48" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F48">
-        <v>27.23</v>
+        <v>27.234</v>
       </c>
       <c r="G48" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H48">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I48" s="1">
-        <v>17.15</v>
+        <v>0.63</v>
       </c>
       <c r="J48">
-        <v>0.64</v>
+        <v>17.15742</v>
       </c>
       <c r="K48" s="1">
-        <v>17.43</v>
-      </c>
-      <c r="L48" t="s">
-        <v>81</v>
-      </c>
-      <c r="M48">
+        <v>0.64</v>
+      </c>
+      <c r="L48" s="1">
+        <v>17.42976</v>
+      </c>
+      <c r="M48" t="s">
+        <v>82</v>
+      </c>
+      <c r="N48">
         <v>214253</v>
       </c>
-      <c r="N48" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14">
+      <c r="O48" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15">
       <c r="A49" s="3">
         <v>46233</v>
       </c>
       <c r="B49" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C49" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D49" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E49" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F49">
-        <v>28.73</v>
+        <v>28.734</v>
       </c>
       <c r="G49" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H49">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I49" s="1">
-        <v>18.1</v>
+        <v>0.63</v>
       </c>
       <c r="J49">
-        <v>0.64</v>
+        <v>18.10242</v>
       </c>
       <c r="K49" s="1">
-        <v>18.39</v>
-      </c>
-      <c r="L49" t="s">
-        <v>82</v>
-      </c>
-      <c r="M49">
+        <v>0.64</v>
+      </c>
+      <c r="L49" s="1">
+        <v>18.38976</v>
+      </c>
+      <c r="M49" t="s">
+        <v>83</v>
+      </c>
+      <c r="N49">
         <v>191122</v>
       </c>
-      <c r="N49" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14">
+      <c r="O49" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15">
       <c r="A50" s="3">
         <v>46233</v>
       </c>
       <c r="B50" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C50" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D50" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E50" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F50">
-        <v>23.48</v>
+        <v>23.484</v>
       </c>
       <c r="G50" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H50">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I50" s="1">
-        <v>14.79</v>
+        <v>0.63</v>
       </c>
       <c r="J50">
-        <v>0.64</v>
+        <v>14.79492</v>
       </c>
       <c r="K50" s="1">
-        <v>15.03</v>
-      </c>
-      <c r="L50" t="s">
-        <v>83</v>
-      </c>
-      <c r="M50">
+        <v>0.64</v>
+      </c>
+      <c r="L50" s="1">
+        <v>15.02976</v>
+      </c>
+      <c r="M50" t="s">
+        <v>84</v>
+      </c>
+      <c r="N50">
         <v>0</v>
       </c>
-      <c r="N50" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14">
+      <c r="O50" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15">
       <c r="A51" s="3">
         <v>46233</v>
       </c>
       <c r="B51" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C51" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D51" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E51" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F51">
-        <v>20.2</v>
+        <v>20.203</v>
       </c>
       <c r="G51" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H51">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I51" s="1">
-        <v>12.73</v>
+        <v>0.63</v>
       </c>
       <c r="J51">
-        <v>0.64</v>
+        <v>12.72789</v>
       </c>
       <c r="K51" s="1">
-        <v>12.93</v>
-      </c>
-      <c r="L51" t="s">
-        <v>84</v>
-      </c>
-      <c r="M51">
+        <v>0.64</v>
+      </c>
+      <c r="L51" s="1">
+        <v>12.92992</v>
+      </c>
+      <c r="M51" t="s">
+        <v>85</v>
+      </c>
+      <c r="N51">
         <v>0</v>
       </c>
-      <c r="N51" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14">
+      <c r="O51" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15">
       <c r="A52" s="3">
         <v>46233</v>
       </c>
       <c r="B52" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D52" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E52" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F52">
-        <v>24.78</v>
+        <v>24.781</v>
       </c>
       <c r="G52" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H52">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I52" s="1">
-        <v>15.61</v>
+        <v>0.63</v>
       </c>
       <c r="J52">
-        <v>0.64</v>
+        <v>15.61203</v>
       </c>
       <c r="K52" s="1">
-        <v>15.86</v>
-      </c>
-      <c r="L52" t="s">
-        <v>85</v>
-      </c>
-      <c r="M52">
+        <v>0.64</v>
+      </c>
+      <c r="L52" s="1">
+        <v>15.85984</v>
+      </c>
+      <c r="M52" t="s">
+        <v>86</v>
+      </c>
+      <c r="N52">
         <v>0</v>
       </c>
-      <c r="N52" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14">
+      <c r="O52" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15">
       <c r="A53" s="3">
         <v>46234</v>
       </c>
       <c r="B53" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C53" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D53" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E53" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F53">
-        <v>19.62</v>
+        <v>19.625</v>
       </c>
       <c r="G53" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H53">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I53" s="1">
-        <v>12.36</v>
+        <v>0.63</v>
       </c>
       <c r="J53">
-        <v>0.64</v>
+        <v>12.36375</v>
       </c>
       <c r="K53" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="L53" s="1">
         <v>12.56</v>
       </c>
-      <c r="L53" t="s">
-        <v>86</v>
-      </c>
-      <c r="M53">
+      <c r="M53" t="s">
+        <v>87</v>
+      </c>
+      <c r="N53">
         <v>0</v>
       </c>
-      <c r="N53" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14">
+      <c r="O53" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15">
       <c r="A54" s="3">
         <v>46234</v>
       </c>
       <c r="B54" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C54" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D54" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E54" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F54">
-        <v>22.94</v>
+        <v>22.938</v>
       </c>
       <c r="G54" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H54">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="I54" s="1">
-        <v>14.45</v>
+        <v>0.63</v>
       </c>
       <c r="J54">
-        <v>0.64</v>
+        <v>14.45094</v>
       </c>
       <c r="K54" s="1">
-        <v>14.68</v>
-      </c>
-      <c r="L54" t="s">
-        <v>87</v>
-      </c>
-      <c r="M54">
+        <v>0.64</v>
+      </c>
+      <c r="L54" s="1">
+        <v>14.68032</v>
+      </c>
+      <c r="M54" t="s">
+        <v>88</v>
+      </c>
+      <c r="N54">
         <v>0</v>
       </c>
-      <c r="N54" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14">
+      <c r="O54" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15">
       <c r="A57" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -3258,32 +3423,32 @@
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
     </row>
-    <row r="58" spans="1:14">
+    <row r="58" spans="1:15">
       <c r="A58" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15">
       <c r="A59" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B59" s="7">
-        <v>1050.73</v>
+        <v>1050.754</v>
       </c>
       <c r="C59" s="7">
         <v>44</v>
@@ -3292,35 +3457,35 @@
         <v>0.629105</v>
       </c>
       <c r="E59" s="7">
-        <v>661.02</v>
+        <v>661.03</v>
       </c>
       <c r="F59" s="7">
         <v>671.54</v>
       </c>
     </row>
-    <row r="60" spans="1:14">
+    <row r="60" spans="1:15">
       <c r="A60" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B60" s="7">
-        <v>96.89</v>
+        <v>96.88800000000001</v>
       </c>
       <c r="C60" s="7">
         <v>6</v>
       </c>
       <c r="D60" s="8">
-        <v>1.756012</v>
+        <v>1.755994</v>
       </c>
       <c r="E60" s="7">
-        <v>170.14</v>
+        <v>170.13</v>
       </c>
       <c r="F60" s="7">
         <v>174.01</v>
       </c>
     </row>
-    <row r="61" spans="1:14">
+    <row r="61" spans="1:15">
       <c r="A61" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B61" s="7">
         <v>25</v>
@@ -3338,12 +3503,12 @@
         <v>38.3</v>
       </c>
     </row>
-    <row r="62" spans="1:14">
+    <row r="62" spans="1:15">
       <c r="A62" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B62" s="10">
-        <v>1172.62</v>
+        <v>1172.642</v>
       </c>
       <c r="C62" s="10">
         <v>53</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ/ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ/ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="146">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -462,9 +459,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -558,10 +555,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -856,7 +853,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O62"/>
+  <dimension ref="A1:N62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -869,13 +866,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -918,2504 +915,2342 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F2">
         <v>10</v>
       </c>
       <c r="G2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2">
+        <v>1.47</v>
+      </c>
+      <c r="I2" s="1">
+        <v>14.7</v>
+      </c>
+      <c r="J2">
+        <v>1.5</v>
+      </c>
+      <c r="K2" s="1">
+        <v>15</v>
+      </c>
+      <c r="L2" t="s">
         <v>38</v>
       </c>
-      <c r="H2">
-        <v>1.369</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.47</v>
-      </c>
-      <c r="J2">
-        <v>14.7</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L2" s="1">
-        <v>15</v>
-      </c>
-      <c r="M2" t="s">
-        <v>39</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>197441</v>
       </c>
-      <c r="O2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46219</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F3">
         <v>18.365</v>
       </c>
       <c r="G3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3">
+        <v>0.62</v>
+      </c>
+      <c r="I3" s="1">
+        <v>11.386</v>
+      </c>
+      <c r="J3">
+        <v>0.63</v>
+      </c>
+      <c r="K3" s="1">
+        <v>11.57</v>
+      </c>
+      <c r="L3" t="s">
         <v>38</v>
       </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="J3">
-        <v>11.3863</v>
-      </c>
-      <c r="K3" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="L3" s="1">
-        <v>11.56995</v>
-      </c>
-      <c r="M3" t="s">
-        <v>39</v>
-      </c>
-      <c r="N3">
+      <c r="M3">
         <v>197441</v>
       </c>
-      <c r="O3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46219</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F4">
         <v>34.095</v>
       </c>
       <c r="G4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0.62</v>
       </c>
       <c r="I4" s="1">
-        <v>0.62</v>
+        <v>21.139</v>
       </c>
       <c r="J4">
-        <v>21.1389</v>
+        <v>0.63</v>
       </c>
       <c r="K4" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="L4" s="1">
-        <v>21.47985</v>
-      </c>
-      <c r="M4" t="s">
-        <v>40</v>
-      </c>
-      <c r="N4">
+        <v>21.48</v>
+      </c>
+      <c r="L4" t="s">
+        <v>39</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-      <c r="O4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46219</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F5">
         <v>16.71</v>
       </c>
       <c r="G5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H5">
-        <v>1.629</v>
+        <v>1.72</v>
       </c>
       <c r="I5" s="1">
-        <v>1.72</v>
+        <v>28.741</v>
       </c>
       <c r="J5">
-        <v>28.7412</v>
+        <v>1.76</v>
       </c>
       <c r="K5" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L5" s="1">
-        <v>29.4096</v>
-      </c>
-      <c r="M5" t="s">
-        <v>41</v>
-      </c>
-      <c r="N5">
+        <v>29.41</v>
+      </c>
+      <c r="L5" t="s">
+        <v>40</v>
+      </c>
+      <c r="M5">
         <v>72365</v>
       </c>
-      <c r="O5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="N5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
         <v>46219</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F6">
         <v>17.222</v>
       </c>
       <c r="G6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H6">
-        <v>1.629</v>
+        <v>1.72</v>
       </c>
       <c r="I6" s="1">
-        <v>1.72</v>
+        <v>29.622</v>
       </c>
       <c r="J6">
-        <v>29.62184</v>
+        <v>1.76</v>
       </c>
       <c r="K6" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L6" s="1">
-        <v>30.31072</v>
-      </c>
-      <c r="M6" t="s">
-        <v>42</v>
-      </c>
-      <c r="N6">
+        <v>30.311</v>
+      </c>
+      <c r="L6" t="s">
+        <v>41</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
-      <c r="O6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="N6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="3">
         <v>46219</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F7">
         <v>24.143</v>
       </c>
       <c r="G7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>0.62</v>
       </c>
       <c r="I7" s="1">
-        <v>0.62</v>
+        <v>14.969</v>
       </c>
       <c r="J7">
-        <v>14.96866</v>
+        <v>0.63</v>
       </c>
       <c r="K7" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="L7" s="1">
-        <v>15.21009</v>
-      </c>
-      <c r="M7" t="s">
-        <v>43</v>
-      </c>
-      <c r="N7">
+        <v>15.21</v>
+      </c>
+      <c r="L7" t="s">
+        <v>42</v>
+      </c>
+      <c r="M7">
         <v>212759</v>
       </c>
-      <c r="O7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="N7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="3">
         <v>46219</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F8">
         <v>17.492</v>
       </c>
       <c r="G8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>0.62</v>
       </c>
       <c r="I8" s="1">
-        <v>0.62</v>
+        <v>10.845</v>
       </c>
       <c r="J8">
-        <v>10.84504</v>
+        <v>0.63</v>
       </c>
       <c r="K8" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="L8" s="1">
-        <v>11.01996</v>
-      </c>
-      <c r="M8" t="s">
-        <v>44</v>
-      </c>
-      <c r="N8">
+        <v>11.02</v>
+      </c>
+      <c r="L8" t="s">
+        <v>43</v>
+      </c>
+      <c r="M8">
         <v>0</v>
       </c>
-      <c r="O8" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="N8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="3">
         <v>46220</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F9">
         <v>21.313</v>
       </c>
       <c r="G9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I9" s="1">
-        <v>0.63</v>
+        <v>13.427</v>
       </c>
       <c r="J9">
-        <v>13.42719</v>
+        <v>0.64</v>
       </c>
       <c r="K9" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L9" s="1">
-        <v>13.64032</v>
-      </c>
-      <c r="M9" t="s">
-        <v>45</v>
-      </c>
-      <c r="N9">
+        <v>13.64</v>
+      </c>
+      <c r="L9" t="s">
+        <v>44</v>
+      </c>
+      <c r="M9">
         <v>0</v>
       </c>
-      <c r="O9" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="N9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="3">
         <v>46220</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F10">
         <v>23.938</v>
       </c>
       <c r="G10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I10" s="1">
-        <v>0.63</v>
+        <v>15.081</v>
       </c>
       <c r="J10">
-        <v>15.08094</v>
+        <v>0.64</v>
       </c>
       <c r="K10" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L10" s="1">
-        <v>15.32032</v>
-      </c>
-      <c r="M10" t="s">
-        <v>46</v>
-      </c>
-      <c r="N10">
+        <v>15.32</v>
+      </c>
+      <c r="L10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M10">
         <v>0</v>
       </c>
-      <c r="O10" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="N10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="3">
         <v>46220</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F11">
         <v>20.234</v>
       </c>
       <c r="G11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I11" s="1">
-        <v>0.63</v>
+        <v>12.747</v>
       </c>
       <c r="J11">
-        <v>12.74742</v>
+        <v>0.64</v>
       </c>
       <c r="K11" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L11" s="1">
-        <v>12.94976</v>
-      </c>
-      <c r="M11" t="s">
-        <v>47</v>
-      </c>
-      <c r="N11">
+        <v>12.95</v>
+      </c>
+      <c r="L11" t="s">
+        <v>46</v>
+      </c>
+      <c r="M11">
         <v>190762</v>
       </c>
-      <c r="O11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="N11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="3">
         <v>46221</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F12">
         <v>21.266</v>
       </c>
       <c r="G12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I12" s="1">
-        <v>0.63</v>
+        <v>13.398</v>
       </c>
       <c r="J12">
-        <v>13.39758</v>
+        <v>0.64</v>
       </c>
       <c r="K12" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L12" s="1">
-        <v>13.61024</v>
-      </c>
-      <c r="M12" t="s">
-        <v>48</v>
-      </c>
-      <c r="N12">
+        <v>13.61</v>
+      </c>
+      <c r="L12" t="s">
+        <v>47</v>
+      </c>
+      <c r="M12">
         <v>197554</v>
       </c>
-      <c r="O12" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+      <c r="N12" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="3">
         <v>46221</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F13">
         <v>21.766</v>
       </c>
       <c r="G13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I13" s="1">
-        <v>0.63</v>
+        <v>13.713</v>
       </c>
       <c r="J13">
-        <v>13.71258</v>
+        <v>0.64</v>
       </c>
       <c r="K13" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L13" s="1">
-        <v>13.93024</v>
-      </c>
-      <c r="M13" t="s">
-        <v>49</v>
-      </c>
-      <c r="N13">
+        <v>13.93</v>
+      </c>
+      <c r="L13" t="s">
+        <v>48</v>
+      </c>
+      <c r="M13">
         <v>212998</v>
       </c>
-      <c r="O13" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+      <c r="N13" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="3">
         <v>46221</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F14">
         <v>20.672</v>
       </c>
       <c r="G14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I14" s="1">
-        <v>0.63</v>
+        <v>13.023</v>
       </c>
       <c r="J14">
-        <v>13.02336</v>
+        <v>0.64</v>
       </c>
       <c r="K14" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L14" s="1">
-        <v>13.23008</v>
-      </c>
-      <c r="M14" t="s">
-        <v>49</v>
-      </c>
-      <c r="N14">
+        <v>13.23</v>
+      </c>
+      <c r="L14" t="s">
+        <v>48</v>
+      </c>
+      <c r="M14">
         <v>0</v>
       </c>
-      <c r="O14" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+      <c r="N14" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="3">
         <v>46222</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F15">
         <v>15.016</v>
       </c>
       <c r="G15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I15" s="1">
-        <v>0.63</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="J15">
-        <v>9.46008</v>
+        <v>0.64</v>
       </c>
       <c r="K15" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L15" s="1">
-        <v>9.610239999999999</v>
-      </c>
-      <c r="M15" t="s">
-        <v>50</v>
-      </c>
-      <c r="N15">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="L15" t="s">
+        <v>49</v>
+      </c>
+      <c r="M15">
         <v>0</v>
       </c>
-      <c r="O15" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+      <c r="N15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="3">
         <v>46222</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F16">
         <v>22.344</v>
       </c>
       <c r="G16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I16" s="1">
-        <v>0.63</v>
+        <v>14.077</v>
       </c>
       <c r="J16">
-        <v>14.07672</v>
+        <v>0.64</v>
       </c>
       <c r="K16" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L16" s="1">
-        <v>14.30016</v>
-      </c>
-      <c r="M16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N16">
+        <v>14.3</v>
+      </c>
+      <c r="L16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16">
         <v>0</v>
       </c>
-      <c r="O16" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+      <c r="N16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="3">
         <v>46223</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F17">
         <v>31.953</v>
       </c>
       <c r="G17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I17" s="1">
-        <v>0.63</v>
+        <v>20.13</v>
       </c>
       <c r="J17">
-        <v>20.13039</v>
+        <v>0.64</v>
       </c>
       <c r="K17" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L17" s="1">
-        <v>20.44992</v>
-      </c>
-      <c r="M17" t="s">
-        <v>52</v>
-      </c>
-      <c r="N17">
+        <v>20.45</v>
+      </c>
+      <c r="L17" t="s">
+        <v>51</v>
+      </c>
+      <c r="M17">
         <v>0</v>
       </c>
-      <c r="O17" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
+      <c r="N17" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="3">
         <v>46223</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F18">
         <v>30.469</v>
       </c>
       <c r="G18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I18" s="1">
-        <v>0.63</v>
+        <v>19.195</v>
       </c>
       <c r="J18">
-        <v>19.19547</v>
+        <v>0.64</v>
       </c>
       <c r="K18" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L18" s="1">
-        <v>19.50016</v>
-      </c>
-      <c r="M18" t="s">
-        <v>53</v>
-      </c>
-      <c r="N18">
+        <v>19.5</v>
+      </c>
+      <c r="L18" t="s">
+        <v>52</v>
+      </c>
+      <c r="M18">
         <v>213276</v>
       </c>
-      <c r="O18" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
+      <c r="N18" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" s="3">
         <v>46223</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F19">
         <v>22.313</v>
       </c>
       <c r="G19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I19" s="1">
-        <v>0.63</v>
+        <v>14.057</v>
       </c>
       <c r="J19">
-        <v>14.05719</v>
+        <v>0.64</v>
       </c>
       <c r="K19" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L19" s="1">
-        <v>14.28032</v>
-      </c>
-      <c r="M19" t="s">
-        <v>54</v>
-      </c>
-      <c r="N19">
+        <v>14.28</v>
+      </c>
+      <c r="L19" t="s">
+        <v>53</v>
+      </c>
+      <c r="M19">
         <v>197721</v>
       </c>
-      <c r="O19" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
+      <c r="N19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="3">
         <v>46223</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F20">
         <v>15.344</v>
       </c>
       <c r="G20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I20" s="1">
-        <v>0.63</v>
+        <v>9.667</v>
       </c>
       <c r="J20">
-        <v>9.66672</v>
+        <v>0.64</v>
       </c>
       <c r="K20" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L20" s="1">
-        <v>9.82016</v>
-      </c>
-      <c r="M20" t="s">
-        <v>55</v>
-      </c>
-      <c r="N20">
+        <v>9.82</v>
+      </c>
+      <c r="L20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M20">
         <v>179669</v>
       </c>
-      <c r="O20" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
+      <c r="N20" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="3">
         <v>46224</v>
       </c>
       <c r="B21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F21">
         <v>28.359</v>
       </c>
       <c r="G21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I21" s="1">
-        <v>0.63</v>
+        <v>17.866</v>
       </c>
       <c r="J21">
-        <v>17.86617</v>
+        <v>0.64</v>
       </c>
       <c r="K21" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L21" s="1">
-        <v>18.14976</v>
-      </c>
-      <c r="M21" t="s">
-        <v>56</v>
-      </c>
-      <c r="N21">
+        <v>18.15</v>
+      </c>
+      <c r="L21" t="s">
+        <v>55</v>
+      </c>
+      <c r="M21">
         <v>155523</v>
       </c>
-      <c r="O21" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
+      <c r="N21" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" s="3">
         <v>46224</v>
       </c>
       <c r="B22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F22">
         <v>28.5</v>
       </c>
       <c r="G22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I22" s="1">
-        <v>0.63</v>
+        <v>17.955</v>
       </c>
       <c r="J22">
-        <v>17.955</v>
+        <v>0.64</v>
       </c>
       <c r="K22" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L22" s="1">
         <v>18.24</v>
       </c>
-      <c r="M22" t="s">
-        <v>57</v>
-      </c>
-      <c r="N22">
+      <c r="L22" t="s">
+        <v>56</v>
+      </c>
+      <c r="M22">
         <v>0</v>
       </c>
-      <c r="O22" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
+      <c r="N22" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" s="3">
         <v>46225</v>
       </c>
       <c r="B23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F23">
         <v>32.109</v>
       </c>
       <c r="G23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I23" s="1">
-        <v>0.63</v>
+        <v>20.229</v>
       </c>
       <c r="J23">
-        <v>20.22867</v>
+        <v>0.64</v>
       </c>
       <c r="K23" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L23" s="1">
-        <v>20.54976</v>
-      </c>
-      <c r="M23" t="s">
-        <v>58</v>
-      </c>
-      <c r="N23">
+        <v>20.55</v>
+      </c>
+      <c r="L23" t="s">
+        <v>57</v>
+      </c>
+      <c r="M23">
         <v>0</v>
       </c>
-      <c r="O23" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
+      <c r="N23" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="3">
         <v>46225</v>
       </c>
       <c r="B24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F24">
         <v>23.797</v>
       </c>
       <c r="G24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I24" s="1">
-        <v>0.63</v>
+        <v>14.992</v>
       </c>
       <c r="J24">
-        <v>14.99211</v>
+        <v>0.64</v>
       </c>
       <c r="K24" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L24" s="1">
-        <v>15.23008</v>
-      </c>
-      <c r="M24" t="s">
-        <v>59</v>
-      </c>
-      <c r="N24">
+        <v>15.23</v>
+      </c>
+      <c r="L24" t="s">
+        <v>58</v>
+      </c>
+      <c r="M24">
         <v>0</v>
       </c>
-      <c r="O24" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
+      <c r="N24" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" s="3">
         <v>46225</v>
       </c>
       <c r="B25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D25" t="s">
+        <v>33</v>
+      </c>
+      <c r="E25" t="s">
         <v>34</v>
-      </c>
-      <c r="E25" t="s">
-        <v>35</v>
       </c>
       <c r="F25">
         <v>5</v>
       </c>
       <c r="G25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H25">
-        <v>1.401</v>
+        <v>1.51</v>
       </c>
       <c r="I25" s="1">
-        <v>1.51</v>
+        <v>7.55</v>
       </c>
       <c r="J25">
-        <v>7.55</v>
+        <v>1.54</v>
       </c>
       <c r="K25" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L25" s="1">
         <v>7.7</v>
       </c>
-      <c r="M25" t="s">
-        <v>60</v>
-      </c>
-      <c r="N25">
+      <c r="L25" t="s">
+        <v>59</v>
+      </c>
+      <c r="M25">
         <v>0</v>
       </c>
-      <c r="O25" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
+      <c r="N25" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" s="3">
         <v>46226</v>
       </c>
       <c r="B26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F26">
         <v>23.328</v>
       </c>
       <c r="G26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I26" s="1">
-        <v>0.63</v>
+        <v>14.697</v>
       </c>
       <c r="J26">
-        <v>14.69664</v>
+        <v>0.64</v>
       </c>
       <c r="K26" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L26" s="1">
-        <v>14.92992</v>
-      </c>
-      <c r="M26" t="s">
-        <v>61</v>
-      </c>
-      <c r="N26">
+        <v>14.93</v>
+      </c>
+      <c r="L26" t="s">
+        <v>60</v>
+      </c>
+      <c r="M26">
         <v>197837</v>
       </c>
-      <c r="O26" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15">
+      <c r="N26" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" s="3">
         <v>46226</v>
       </c>
       <c r="B27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F27">
         <v>20.203</v>
       </c>
       <c r="G27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I27" s="1">
-        <v>0.63</v>
+        <v>12.728</v>
       </c>
       <c r="J27">
-        <v>12.72789</v>
+        <v>0.64</v>
       </c>
       <c r="K27" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L27" s="1">
-        <v>12.92992</v>
-      </c>
-      <c r="M27" t="s">
-        <v>62</v>
-      </c>
-      <c r="N27">
+        <v>12.93</v>
+      </c>
+      <c r="L27" t="s">
+        <v>61</v>
+      </c>
+      <c r="M27">
         <v>179911</v>
       </c>
-      <c r="O27" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15">
+      <c r="N27" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" s="3">
         <v>46227</v>
       </c>
       <c r="B28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E28" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F28">
         <v>20.563</v>
       </c>
       <c r="G28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H28">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I28" s="1">
-        <v>0.63</v>
+        <v>12.955</v>
       </c>
       <c r="J28">
-        <v>12.95469</v>
+        <v>0.64</v>
       </c>
       <c r="K28" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L28" s="1">
-        <v>13.16032</v>
-      </c>
-      <c r="M28" t="s">
-        <v>63</v>
-      </c>
-      <c r="N28">
+        <v>13.16</v>
+      </c>
+      <c r="L28" t="s">
+        <v>62</v>
+      </c>
+      <c r="M28">
         <v>0</v>
       </c>
-      <c r="O28" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15">
+      <c r="N28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" s="3">
         <v>46227</v>
       </c>
       <c r="B29" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F29">
         <v>26.906</v>
       </c>
       <c r="G29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I29" s="1">
-        <v>0.63</v>
+        <v>16.951</v>
       </c>
       <c r="J29">
-        <v>16.95078</v>
+        <v>0.64</v>
       </c>
       <c r="K29" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L29" s="1">
-        <v>17.21984</v>
-      </c>
-      <c r="M29" t="s">
-        <v>64</v>
-      </c>
-      <c r="N29">
+        <v>17.22</v>
+      </c>
+      <c r="L29" t="s">
+        <v>63</v>
+      </c>
+      <c r="M29">
         <v>0</v>
       </c>
-      <c r="O29" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15">
+      <c r="N29" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" s="3">
         <v>46228</v>
       </c>
       <c r="B30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F30">
         <v>26.625</v>
       </c>
       <c r="G30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I30" s="1">
-        <v>0.63</v>
+        <v>16.774</v>
       </c>
       <c r="J30">
-        <v>16.77375</v>
+        <v>0.64</v>
       </c>
       <c r="K30" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L30" s="1">
         <v>17.04</v>
       </c>
-      <c r="M30" t="s">
-        <v>65</v>
-      </c>
-      <c r="N30">
+      <c r="L30" t="s">
+        <v>64</v>
+      </c>
+      <c r="M30">
         <v>180198</v>
       </c>
-      <c r="O30" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15">
+      <c r="N30" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" s="3">
         <v>46228</v>
       </c>
       <c r="B31" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C31" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D31" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E31" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F31">
         <v>16</v>
       </c>
       <c r="G31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H31">
-        <v>1.649</v>
+        <v>1.77</v>
       </c>
       <c r="I31" s="1">
-        <v>1.77</v>
+        <v>28.32</v>
       </c>
       <c r="J31">
-        <v>28.32</v>
+        <v>1.81</v>
       </c>
       <c r="K31" s="1">
-        <v>1.81</v>
-      </c>
-      <c r="L31" s="1">
         <v>28.96</v>
       </c>
-      <c r="M31" t="s">
-        <v>66</v>
-      </c>
-      <c r="N31">
+      <c r="L31" t="s">
+        <v>65</v>
+      </c>
+      <c r="M31">
         <v>72540</v>
       </c>
-      <c r="O31" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15">
+      <c r="N31" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" s="3">
         <v>46228</v>
       </c>
       <c r="B32" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F32">
         <v>13</v>
       </c>
       <c r="G32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H32">
-        <v>1.649</v>
+        <v>1.77</v>
       </c>
       <c r="I32" s="1">
-        <v>1.77</v>
+        <v>23.01</v>
       </c>
       <c r="J32">
-        <v>23.01</v>
+        <v>1.81</v>
       </c>
       <c r="K32" s="1">
-        <v>1.81</v>
-      </c>
-      <c r="L32" s="1">
         <v>23.53</v>
       </c>
-      <c r="M32" t="s">
-        <v>66</v>
-      </c>
-      <c r="N32">
+      <c r="L32" t="s">
+        <v>65</v>
+      </c>
+      <c r="M32">
         <v>72840</v>
       </c>
-      <c r="O32" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15">
+      <c r="N32" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" s="3">
         <v>46228</v>
       </c>
       <c r="B33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C33" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D33" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F33">
         <v>22.406</v>
       </c>
       <c r="G33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I33" s="1">
-        <v>0.63</v>
+        <v>14.116</v>
       </c>
       <c r="J33">
-        <v>14.11578</v>
+        <v>0.64</v>
       </c>
       <c r="K33" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L33" s="1">
-        <v>14.33984</v>
-      </c>
-      <c r="M33" t="s">
-        <v>67</v>
-      </c>
-      <c r="N33">
+        <v>14.34</v>
+      </c>
+      <c r="L33" t="s">
+        <v>66</v>
+      </c>
+      <c r="M33">
         <v>213871</v>
       </c>
-      <c r="O33" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15">
+      <c r="N33" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" s="3">
         <v>46229</v>
       </c>
       <c r="B34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E34" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F34">
         <v>21.813</v>
       </c>
       <c r="G34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I34" s="1">
-        <v>0.63</v>
+        <v>13.742</v>
       </c>
       <c r="J34">
-        <v>13.74219</v>
+        <v>0.64</v>
       </c>
       <c r="K34" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L34" s="1">
-        <v>13.96032</v>
-      </c>
-      <c r="M34" t="s">
-        <v>68</v>
-      </c>
-      <c r="N34">
+        <v>13.96</v>
+      </c>
+      <c r="L34" t="s">
+        <v>67</v>
+      </c>
+      <c r="M34">
         <v>0</v>
       </c>
-      <c r="O34" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15">
+      <c r="N34" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" s="3">
         <v>46229</v>
       </c>
       <c r="B35" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F35">
         <v>25.609</v>
       </c>
       <c r="G35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I35" s="1">
-        <v>0.63</v>
+        <v>16.134</v>
       </c>
       <c r="J35">
-        <v>16.13367</v>
+        <v>0.64</v>
       </c>
       <c r="K35" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L35" s="1">
-        <v>16.38976</v>
-      </c>
-      <c r="M35" t="s">
-        <v>69</v>
-      </c>
-      <c r="N35">
+        <v>16.39</v>
+      </c>
+      <c r="L35" t="s">
+        <v>68</v>
+      </c>
+      <c r="M35">
         <v>0</v>
       </c>
-      <c r="O35" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15">
+      <c r="N35" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" s="3">
         <v>46229</v>
       </c>
       <c r="B36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C36" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F36">
         <v>21.875</v>
       </c>
       <c r="G36" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I36" s="1">
-        <v>0.63</v>
+        <v>13.781</v>
       </c>
       <c r="J36">
-        <v>13.78125</v>
+        <v>0.64</v>
       </c>
       <c r="K36" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L36" s="1">
         <v>14</v>
       </c>
-      <c r="M36" t="s">
-        <v>70</v>
-      </c>
-      <c r="N36">
+      <c r="L36" t="s">
+        <v>69</v>
+      </c>
+      <c r="M36">
         <v>0</v>
       </c>
-      <c r="O36" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15">
+      <c r="N36" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37" s="3">
         <v>46229</v>
       </c>
       <c r="B37" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C37" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D37" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E37" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F37">
         <v>17.094</v>
       </c>
       <c r="G37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H37">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I37" s="1">
-        <v>0.63</v>
+        <v>10.769</v>
       </c>
       <c r="J37">
-        <v>10.76922</v>
+        <v>0.64</v>
       </c>
       <c r="K37" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L37" s="1">
-        <v>10.94016</v>
-      </c>
-      <c r="M37" t="s">
-        <v>71</v>
-      </c>
-      <c r="N37">
+        <v>10.94</v>
+      </c>
+      <c r="L37" t="s">
+        <v>70</v>
+      </c>
+      <c r="M37">
         <v>197920</v>
       </c>
-      <c r="O37" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15">
+      <c r="N37" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" s="3">
         <v>46230</v>
       </c>
       <c r="B38" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F38">
         <v>25.891</v>
       </c>
       <c r="G38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H38">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I38" s="1">
-        <v>0.63</v>
+        <v>16.311</v>
       </c>
       <c r="J38">
-        <v>16.31133</v>
+        <v>0.64</v>
       </c>
       <c r="K38" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L38" s="1">
-        <v>16.57024</v>
-      </c>
-      <c r="M38" t="s">
-        <v>72</v>
-      </c>
-      <c r="N38">
+        <v>16.57</v>
+      </c>
+      <c r="L38" t="s">
+        <v>71</v>
+      </c>
+      <c r="M38">
         <v>0</v>
       </c>
-      <c r="O38" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15">
+      <c r="N38" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39" s="3">
         <v>46230</v>
       </c>
       <c r="B39" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C39" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E39" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F39">
         <v>25.766</v>
       </c>
       <c r="G39" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H39">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I39" s="1">
-        <v>0.63</v>
+        <v>16.233</v>
       </c>
       <c r="J39">
-        <v>16.23258</v>
+        <v>0.64</v>
       </c>
       <c r="K39" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L39" s="1">
-        <v>16.49024</v>
-      </c>
-      <c r="M39" t="s">
-        <v>73</v>
-      </c>
-      <c r="N39">
+        <v>16.49</v>
+      </c>
+      <c r="L39" t="s">
+        <v>72</v>
+      </c>
+      <c r="M39">
         <v>198059</v>
       </c>
-      <c r="O39" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15">
+      <c r="N39" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40" s="3">
         <v>46231</v>
       </c>
       <c r="B40" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C40" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D40" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E40" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F40">
         <v>10</v>
       </c>
       <c r="G40" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H40">
-        <v>1.441</v>
+        <v>1.53</v>
       </c>
       <c r="I40" s="1">
-        <v>1.53</v>
+        <v>15.3</v>
       </c>
       <c r="J40">
-        <v>15.3</v>
+        <v>1.56</v>
       </c>
       <c r="K40" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L40" s="1">
         <v>15.6</v>
       </c>
-      <c r="M40" t="s">
-        <v>74</v>
-      </c>
-      <c r="N40">
+      <c r="L40" t="s">
+        <v>73</v>
+      </c>
+      <c r="M40">
         <v>0</v>
       </c>
-      <c r="O40" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15">
+      <c r="N40" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41" s="3">
         <v>46231</v>
       </c>
       <c r="B41" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C41" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D41" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E41" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F41">
         <v>36.453</v>
       </c>
       <c r="G41" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H41">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I41" s="1">
-        <v>0.63</v>
+        <v>22.965</v>
       </c>
       <c r="J41">
-        <v>22.96539</v>
+        <v>0.64</v>
       </c>
       <c r="K41" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L41" s="1">
-        <v>23.32992</v>
-      </c>
-      <c r="M41" t="s">
-        <v>75</v>
-      </c>
-      <c r="N41">
+        <v>23.33</v>
+      </c>
+      <c r="L41" t="s">
+        <v>74</v>
+      </c>
+      <c r="M41">
         <v>0</v>
       </c>
-      <c r="O41" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15">
+      <c r="N41" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42" s="3">
         <v>46231</v>
       </c>
       <c r="B42" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C42" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D42" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E42" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F42">
         <v>16.319</v>
       </c>
       <c r="G42" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H42">
-        <v>1.669</v>
+        <v>1.78</v>
       </c>
       <c r="I42" s="1">
-        <v>1.78</v>
+        <v>29.048</v>
       </c>
       <c r="J42">
-        <v>29.04782</v>
+        <v>1.82</v>
       </c>
       <c r="K42" s="1">
-        <v>1.82</v>
-      </c>
-      <c r="L42" s="1">
-        <v>29.70058</v>
-      </c>
-      <c r="M42" t="s">
-        <v>76</v>
-      </c>
-      <c r="N42">
+        <v>29.701</v>
+      </c>
+      <c r="L42" t="s">
+        <v>75</v>
+      </c>
+      <c r="M42">
         <v>73026</v>
       </c>
-      <c r="O42" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15">
+      <c r="N42" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
       <c r="A43" s="3">
         <v>46231</v>
       </c>
       <c r="B43" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C43" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D43" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E43" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F43">
         <v>27.766</v>
       </c>
       <c r="G43" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H43">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I43" s="1">
-        <v>0.63</v>
+        <v>17.493</v>
       </c>
       <c r="J43">
-        <v>17.49258</v>
+        <v>0.64</v>
       </c>
       <c r="K43" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L43" s="1">
-        <v>17.77024</v>
-      </c>
-      <c r="M43" t="s">
-        <v>77</v>
-      </c>
-      <c r="N43">
+        <v>17.77</v>
+      </c>
+      <c r="L43" t="s">
+        <v>76</v>
+      </c>
+      <c r="M43">
         <v>198198</v>
       </c>
-      <c r="O43" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15">
+      <c r="N43" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44" s="3">
         <v>46231</v>
       </c>
       <c r="B44" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C44" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D44" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E44" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F44">
         <v>17.637</v>
       </c>
       <c r="G44" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H44">
-        <v>1.669</v>
+        <v>1.78</v>
       </c>
       <c r="I44" s="1">
-        <v>1.78</v>
+        <v>31.394</v>
       </c>
       <c r="J44">
-        <v>31.39386</v>
+        <v>1.82</v>
       </c>
       <c r="K44" s="1">
-        <v>1.82</v>
-      </c>
-      <c r="L44" s="1">
-        <v>32.09934</v>
-      </c>
-      <c r="M44" t="s">
-        <v>78</v>
-      </c>
-      <c r="N44">
+        <v>32.099</v>
+      </c>
+      <c r="L44" t="s">
+        <v>77</v>
+      </c>
+      <c r="M44">
         <v>0</v>
       </c>
-      <c r="O44" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15">
+      <c r="N44" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
       <c r="A45" s="3">
         <v>46231</v>
       </c>
       <c r="B45" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C45" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D45" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E45" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F45">
         <v>23.047</v>
       </c>
       <c r="G45" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H45">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I45" s="1">
-        <v>0.63</v>
+        <v>14.52</v>
       </c>
       <c r="J45">
-        <v>14.51961</v>
+        <v>0.64</v>
       </c>
       <c r="K45" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L45" s="1">
-        <v>14.75008</v>
-      </c>
-      <c r="M45" t="s">
-        <v>79</v>
-      </c>
-      <c r="N45">
+        <v>14.75</v>
+      </c>
+      <c r="L45" t="s">
+        <v>78</v>
+      </c>
+      <c r="M45">
         <v>0</v>
       </c>
-      <c r="O45" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15">
+      <c r="N45" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
       <c r="A46" s="3">
         <v>46231</v>
       </c>
       <c r="B46" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C46" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D46" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E46" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F46">
         <v>24.656</v>
       </c>
       <c r="G46" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H46">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I46" s="1">
-        <v>0.63</v>
+        <v>15.533</v>
       </c>
       <c r="J46">
-        <v>15.53328</v>
+        <v>0.64</v>
       </c>
       <c r="K46" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L46" s="1">
-        <v>15.77984</v>
-      </c>
-      <c r="M46" t="s">
-        <v>80</v>
-      </c>
-      <c r="N46">
+        <v>15.78</v>
+      </c>
+      <c r="L46" t="s">
+        <v>79</v>
+      </c>
+      <c r="M46">
         <v>180491</v>
       </c>
-      <c r="O46" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15">
+      <c r="N46" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
       <c r="A47" s="3">
         <v>46232</v>
       </c>
       <c r="B47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C47" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D47" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E47" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F47">
         <v>20.266</v>
       </c>
       <c r="G47" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H47">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I47" s="1">
-        <v>0.63</v>
+        <v>12.768</v>
       </c>
       <c r="J47">
-        <v>12.76758</v>
+        <v>0.64</v>
       </c>
       <c r="K47" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L47" s="1">
-        <v>12.97024</v>
-      </c>
-      <c r="M47" t="s">
-        <v>81</v>
-      </c>
-      <c r="N47">
+        <v>12.97</v>
+      </c>
+      <c r="L47" t="s">
+        <v>80</v>
+      </c>
+      <c r="M47">
         <v>198312</v>
       </c>
-      <c r="O47" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15">
+      <c r="N47" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
       <c r="A48" s="3">
         <v>46232</v>
       </c>
       <c r="B48" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C48" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D48" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E48" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F48">
         <v>27.234</v>
       </c>
       <c r="G48" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H48">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I48" s="1">
-        <v>0.63</v>
+        <v>17.157</v>
       </c>
       <c r="J48">
-        <v>17.15742</v>
+        <v>0.64</v>
       </c>
       <c r="K48" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L48" s="1">
-        <v>17.42976</v>
-      </c>
-      <c r="M48" t="s">
-        <v>82</v>
-      </c>
-      <c r="N48">
+        <v>17.43</v>
+      </c>
+      <c r="L48" t="s">
+        <v>81</v>
+      </c>
+      <c r="M48">
         <v>214253</v>
       </c>
-      <c r="O48" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15">
+      <c r="N48" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
       <c r="A49" s="3">
         <v>46233</v>
       </c>
       <c r="B49" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D49" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E49" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F49">
         <v>28.734</v>
       </c>
       <c r="G49" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H49">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I49" s="1">
-        <v>0.63</v>
+        <v>18.102</v>
       </c>
       <c r="J49">
-        <v>18.10242</v>
+        <v>0.64</v>
       </c>
       <c r="K49" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L49" s="1">
-        <v>18.38976</v>
-      </c>
-      <c r="M49" t="s">
-        <v>83</v>
-      </c>
-      <c r="N49">
+        <v>18.39</v>
+      </c>
+      <c r="L49" t="s">
+        <v>82</v>
+      </c>
+      <c r="M49">
         <v>191122</v>
       </c>
-      <c r="O49" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15">
+      <c r="N49" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
       <c r="A50" s="3">
         <v>46233</v>
       </c>
       <c r="B50" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C50" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D50" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E50" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F50">
         <v>23.484</v>
       </c>
       <c r="G50" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I50" s="1">
-        <v>0.63</v>
+        <v>14.795</v>
       </c>
       <c r="J50">
-        <v>14.79492</v>
+        <v>0.64</v>
       </c>
       <c r="K50" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L50" s="1">
-        <v>15.02976</v>
-      </c>
-      <c r="M50" t="s">
-        <v>84</v>
-      </c>
-      <c r="N50">
+        <v>15.03</v>
+      </c>
+      <c r="L50" t="s">
+        <v>83</v>
+      </c>
+      <c r="M50">
         <v>0</v>
       </c>
-      <c r="O50" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15">
+      <c r="N50" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
       <c r="A51" s="3">
         <v>46233</v>
       </c>
       <c r="B51" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C51" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D51" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E51" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F51">
         <v>20.203</v>
       </c>
       <c r="G51" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H51">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I51" s="1">
-        <v>0.63</v>
+        <v>12.728</v>
       </c>
       <c r="J51">
-        <v>12.72789</v>
+        <v>0.64</v>
       </c>
       <c r="K51" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L51" s="1">
-        <v>12.92992</v>
-      </c>
-      <c r="M51" t="s">
-        <v>85</v>
-      </c>
-      <c r="N51">
+        <v>12.93</v>
+      </c>
+      <c r="L51" t="s">
+        <v>84</v>
+      </c>
+      <c r="M51">
         <v>0</v>
       </c>
-      <c r="O51" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15">
+      <c r="N51" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
       <c r="A52" s="3">
         <v>46233</v>
       </c>
       <c r="B52" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C52" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D52" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E52" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F52">
         <v>24.781</v>
       </c>
       <c r="G52" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H52">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I52" s="1">
-        <v>0.63</v>
+        <v>15.612</v>
       </c>
       <c r="J52">
-        <v>15.61203</v>
+        <v>0.64</v>
       </c>
       <c r="K52" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L52" s="1">
-        <v>15.85984</v>
-      </c>
-      <c r="M52" t="s">
-        <v>86</v>
-      </c>
-      <c r="N52">
+        <v>15.86</v>
+      </c>
+      <c r="L52" t="s">
+        <v>85</v>
+      </c>
+      <c r="M52">
         <v>0</v>
       </c>
-      <c r="O52" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15">
+      <c r="N52" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
       <c r="A53" s="3">
         <v>46234</v>
       </c>
       <c r="B53" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C53" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D53" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E53" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F53">
         <v>19.625</v>
       </c>
       <c r="G53" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H53">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I53" s="1">
-        <v>0.63</v>
+        <v>12.364</v>
       </c>
       <c r="J53">
-        <v>12.36375</v>
+        <v>0.64</v>
       </c>
       <c r="K53" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L53" s="1">
         <v>12.56</v>
       </c>
-      <c r="M53" t="s">
-        <v>87</v>
-      </c>
-      <c r="N53">
+      <c r="L53" t="s">
+        <v>86</v>
+      </c>
+      <c r="M53">
         <v>0</v>
       </c>
-      <c r="O53" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15">
+      <c r="N53" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
       <c r="A54" s="3">
         <v>46234</v>
       </c>
       <c r="B54" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C54" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D54" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E54" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F54">
         <v>22.938</v>
       </c>
       <c r="G54" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H54">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I54" s="1">
-        <v>0.63</v>
+        <v>14.451</v>
       </c>
       <c r="J54">
-        <v>14.45094</v>
+        <v>0.64</v>
       </c>
       <c r="K54" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L54" s="1">
-        <v>14.68032</v>
-      </c>
-      <c r="M54" t="s">
-        <v>88</v>
-      </c>
-      <c r="N54">
+        <v>14.68</v>
+      </c>
+      <c r="L54" t="s">
+        <v>87</v>
+      </c>
+      <c r="M54">
         <v>0</v>
       </c>
-      <c r="O54" t="s">
+      <c r="N54" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
+      <c r="A57" s="4" t="s">
         <v>140</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15">
-      <c r="A57" s="4" t="s">
-        <v>141</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -3423,89 +3258,89 @@
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
     </row>
-    <row r="58" spans="1:15">
+    <row r="58" spans="1:14">
       <c r="A58" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B58" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="C58" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="D58" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="D58" s="5" t="s">
-        <v>145</v>
-      </c>
       <c r="E58" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14">
       <c r="A59" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B59" s="7">
         <v>1050.754</v>
       </c>
-      <c r="C59" s="7">
+      <c r="C59" s="8">
         <v>44</v>
       </c>
       <c r="D59" s="8">
-        <v>0.629105</v>
-      </c>
-      <c r="E59" s="7">
-        <v>661.03</v>
-      </c>
-      <c r="F59" s="7">
+        <v>0.629</v>
+      </c>
+      <c r="E59" s="8">
+        <v>661.035</v>
+      </c>
+      <c r="F59" s="8">
         <v>671.54</v>
       </c>
     </row>
-    <row r="60" spans="1:15">
+    <row r="60" spans="1:14">
       <c r="A60" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B60" s="7">
         <v>96.88800000000001</v>
       </c>
-      <c r="C60" s="7">
+      <c r="C60" s="8">
         <v>6</v>
       </c>
       <c r="D60" s="8">
-        <v>1.755994</v>
-      </c>
-      <c r="E60" s="7">
-        <v>170.13</v>
-      </c>
-      <c r="F60" s="7">
-        <v>174.01</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15">
+        <v>1.756</v>
+      </c>
+      <c r="E60" s="8">
+        <v>170.135</v>
+      </c>
+      <c r="F60" s="8">
+        <v>174.011</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14">
       <c r="A61" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B61" s="7">
         <v>25</v>
       </c>
-      <c r="C61" s="7">
+      <c r="C61" s="8">
         <v>3</v>
       </c>
       <c r="D61" s="8">
         <v>1.502</v>
       </c>
-      <c r="E61" s="7">
+      <c r="E61" s="8">
         <v>37.55</v>
       </c>
-      <c r="F61" s="7">
+      <c r="F61" s="8">
         <v>38.3</v>
       </c>
     </row>
-    <row r="62" spans="1:15">
+    <row r="62" spans="1:14">
       <c r="A62" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B62" s="10">
         <v>1172.642</v>
@@ -3515,10 +3350,10 @@
       </c>
       <c r="D62" s="8"/>
       <c r="E62" s="10">
-        <v>868.71</v>
+        <v>868.72</v>
       </c>
       <c r="F62" s="10">
-        <v>883.85</v>
+        <v>883.851</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ/ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ/ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ.xlsx
@@ -867,10 +867,10 @@
         <v>37</v>
       </c>
       <c r="H2" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I2" s="1">
-        <v>32.264</v>
+        <v>21.184</v>
       </c>
       <c r="J2" s="1">
         <v>0.66</v>
@@ -911,10 +911,10 @@
         <v>37</v>
       </c>
       <c r="H3" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I3" s="1">
-        <v>17.998</v>
+        <v>11.817</v>
       </c>
       <c r="J3" s="1">
         <v>0.66</v>
@@ -955,10 +955,10 @@
         <v>37</v>
       </c>
       <c r="H4" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I4" s="1">
-        <v>17.563</v>
+        <v>11.531</v>
       </c>
       <c r="J4" s="1">
         <v>0.66</v>
@@ -999,10 +999,10 @@
         <v>37</v>
       </c>
       <c r="H5" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I5" s="1">
-        <v>16.167</v>
+        <v>10.614</v>
       </c>
       <c r="J5" s="1">
         <v>0.66</v>
@@ -1043,10 +1043,10 @@
         <v>37</v>
       </c>
       <c r="H6" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I6" s="1">
-        <v>16.226</v>
+        <v>10.654</v>
       </c>
       <c r="J6" s="1">
         <v>0.66</v>
@@ -1087,10 +1087,10 @@
         <v>37</v>
       </c>
       <c r="H7" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I7" s="1">
-        <v>25.661</v>
+        <v>16.848</v>
       </c>
       <c r="J7" s="1">
         <v>0.66</v>
@@ -1131,10 +1131,10 @@
         <v>37</v>
       </c>
       <c r="H8" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I8" s="1">
-        <v>22.968</v>
+        <v>15.08</v>
       </c>
       <c r="J8" s="1">
         <v>0.66</v>
@@ -1175,10 +1175,10 @@
         <v>37</v>
       </c>
       <c r="H9" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I9" s="1">
-        <v>29.938</v>
+        <v>19.656</v>
       </c>
       <c r="J9" s="1">
         <v>0.66</v>
@@ -1219,10 +1219,10 @@
         <v>37</v>
       </c>
       <c r="H10" s="1">
-        <v>1.656</v>
+        <v>1.78</v>
       </c>
       <c r="I10" s="1">
-        <v>26.496</v>
+        <v>28.48</v>
       </c>
       <c r="J10" s="1">
         <v>1.82</v>
@@ -1263,10 +1263,10 @@
         <v>37</v>
       </c>
       <c r="H11" s="1">
-        <v>1.656</v>
+        <v>1.78</v>
       </c>
       <c r="I11" s="1">
-        <v>29.758</v>
+        <v>31.987</v>
       </c>
       <c r="J11" s="1">
         <v>1.82</v>
@@ -1307,10 +1307,10 @@
         <v>37</v>
       </c>
       <c r="H12" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I12" s="1">
-        <v>22.037</v>
+        <v>14.469</v>
       </c>
       <c r="J12" s="1">
         <v>0.66</v>
@@ -1351,10 +1351,10 @@
         <v>37</v>
       </c>
       <c r="H13" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I13" s="1">
-        <v>30.116</v>
+        <v>19.773</v>
       </c>
       <c r="J13" s="1">
         <v>0.66</v>
@@ -1395,10 +1395,10 @@
         <v>37</v>
       </c>
       <c r="H14" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I14" s="1">
-        <v>17.8</v>
+        <v>11.687</v>
       </c>
       <c r="J14" s="1">
         <v>0.66</v>
@@ -1439,10 +1439,10 @@
         <v>37</v>
       </c>
       <c r="H15" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I15" s="1">
-        <v>27.868</v>
+        <v>18.298</v>
       </c>
       <c r="J15" s="1">
         <v>0.66</v>
@@ -1483,10 +1483,10 @@
         <v>37</v>
       </c>
       <c r="H16" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I16" s="1">
-        <v>30.581</v>
+        <v>20.078</v>
       </c>
       <c r="J16" s="1">
         <v>0.66</v>
@@ -1527,10 +1527,10 @@
         <v>37</v>
       </c>
       <c r="H17" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I17" s="1">
-        <v>23.126</v>
+        <v>15.184</v>
       </c>
       <c r="J17" s="1">
         <v>0.66</v>
@@ -1571,10 +1571,10 @@
         <v>37</v>
       </c>
       <c r="H18" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I18" s="1">
-        <v>25.74</v>
+        <v>16.9</v>
       </c>
       <c r="J18" s="1">
         <v>0.66</v>
@@ -1615,10 +1615,10 @@
         <v>37</v>
       </c>
       <c r="H19" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I19" s="1">
-        <v>21.8</v>
+        <v>14.313</v>
       </c>
       <c r="J19" s="1">
         <v>0.66</v>
@@ -1659,10 +1659,10 @@
         <v>37</v>
       </c>
       <c r="H20" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I20" s="1">
-        <v>22.79</v>
+        <v>14.963</v>
       </c>
       <c r="J20" s="1">
         <v>0.66</v>
@@ -1703,10 +1703,10 @@
         <v>37</v>
       </c>
       <c r="H21" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I21" s="1">
-        <v>25.265</v>
+        <v>16.588</v>
       </c>
       <c r="J21" s="1">
         <v>0.66</v>
@@ -1747,10 +1747,10 @@
         <v>37</v>
       </c>
       <c r="H22" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I22" s="1">
-        <v>24.295</v>
+        <v>15.951</v>
       </c>
       <c r="J22" s="1">
         <v>0.66</v>
@@ -1791,10 +1791,10 @@
         <v>37</v>
       </c>
       <c r="H23" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I23" s="1">
-        <v>27.631</v>
+        <v>18.142</v>
       </c>
       <c r="J23" s="1">
         <v>0.66</v>
@@ -1835,10 +1835,10 @@
         <v>37</v>
       </c>
       <c r="H24" s="1">
-        <v>1.459</v>
+        <v>1.55</v>
       </c>
       <c r="I24" s="1">
-        <v>24.424</v>
+        <v>25.947</v>
       </c>
       <c r="J24" s="1">
         <v>1.58</v>
@@ -1879,10 +1879,10 @@
         <v>37</v>
       </c>
       <c r="H25" s="1">
-        <v>1.459</v>
+        <v>1.55</v>
       </c>
       <c r="I25" s="1">
-        <v>23.081</v>
+        <v>24.521</v>
       </c>
       <c r="J25" s="1">
         <v>1.58</v>
@@ -1923,10 +1923,10 @@
         <v>37</v>
       </c>
       <c r="H26" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I26" s="1">
-        <v>30.027</v>
+        <v>19.714</v>
       </c>
       <c r="J26" s="1">
         <v>0.66</v>
@@ -1967,10 +1967,10 @@
         <v>37</v>
       </c>
       <c r="H27" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I27" s="1">
-        <v>26.096</v>
+        <v>17.134</v>
       </c>
       <c r="J27" s="1">
         <v>0.66</v>
@@ -2011,10 +2011,10 @@
         <v>37</v>
       </c>
       <c r="H28" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I28" s="1">
-        <v>28.106</v>
+        <v>18.454</v>
       </c>
       <c r="J28" s="1">
         <v>0.66</v>
@@ -2055,10 +2055,10 @@
         <v>37</v>
       </c>
       <c r="H29" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I29" s="1">
-        <v>31.413</v>
+        <v>20.624</v>
       </c>
       <c r="J29" s="1">
         <v>0.66</v>
@@ -2099,10 +2099,10 @@
         <v>37</v>
       </c>
       <c r="H30" s="1">
-        <v>1.459</v>
+        <v>1.56</v>
       </c>
       <c r="I30" s="1">
-        <v>17.508</v>
+        <v>18.72</v>
       </c>
       <c r="J30" s="1">
         <v>1.59</v>
@@ -2143,10 +2143,10 @@
         <v>37</v>
       </c>
       <c r="H31" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I31" s="1">
-        <v>35.64</v>
+        <v>23.4</v>
       </c>
       <c r="J31" s="1">
         <v>0.66</v>
@@ -2187,10 +2187,10 @@
         <v>37</v>
       </c>
       <c r="H32" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I32" s="1">
-        <v>14.474</v>
+        <v>9.503</v>
       </c>
       <c r="J32" s="1">
         <v>0.66</v>
@@ -2231,10 +2231,10 @@
         <v>37</v>
       </c>
       <c r="H33" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I33" s="1">
-        <v>28.443</v>
+        <v>18.675</v>
       </c>
       <c r="J33" s="1">
         <v>0.66</v>
@@ -2275,10 +2275,10 @@
         <v>37</v>
       </c>
       <c r="H34" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I34" s="1">
-        <v>22.423</v>
+        <v>14.722</v>
       </c>
       <c r="J34" s="1">
         <v>0.66</v>
@@ -2319,10 +2319,10 @@
         <v>37</v>
       </c>
       <c r="H35" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I35" s="1">
-        <v>16.543</v>
+        <v>10.862</v>
       </c>
       <c r="J35" s="1">
         <v>0.66</v>
@@ -2363,10 +2363,10 @@
         <v>37</v>
       </c>
       <c r="H36" s="1">
-        <v>1.689</v>
+        <v>1.82</v>
       </c>
       <c r="I36" s="1">
-        <v>18.647</v>
+        <v>20.093</v>
       </c>
       <c r="J36" s="1">
         <v>1.86</v>
@@ -2407,10 +2407,10 @@
         <v>37</v>
       </c>
       <c r="H37" s="1">
-        <v>1.689</v>
+        <v>1.82</v>
       </c>
       <c r="I37" s="1">
-        <v>28.882</v>
+        <v>31.122</v>
       </c>
       <c r="J37" s="1">
         <v>1.86</v>
@@ -2451,10 +2451,10 @@
         <v>37</v>
       </c>
       <c r="H38" s="1">
-        <v>1.459</v>
+        <v>1.58</v>
       </c>
       <c r="I38" s="1">
-        <v>7.31</v>
+        <v>7.916</v>
       </c>
       <c r="J38" s="1">
         <v>1.61</v>
@@ -2495,10 +2495,10 @@
         <v>37</v>
       </c>
       <c r="H39" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I39" s="1">
-        <v>29.66</v>
+        <v>19.474</v>
       </c>
       <c r="J39" s="1">
         <v>0.66</v>
@@ -2539,10 +2539,10 @@
         <v>37</v>
       </c>
       <c r="H40" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I40" s="1">
-        <v>24.215</v>
+        <v>15.899</v>
       </c>
       <c r="J40" s="1">
         <v>0.66</v>
@@ -2583,10 +2583,10 @@
         <v>37</v>
       </c>
       <c r="H41" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I41" s="1">
-        <v>26.265</v>
+        <v>17.245</v>
       </c>
       <c r="J41" s="1">
         <v>0.66</v>
@@ -2645,10 +2645,10 @@
         <v>32</v>
       </c>
       <c r="D46" s="9">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="E46" s="7">
-        <v>791.14</v>
+        <v>519.4400000000001</v>
       </c>
       <c r="F46" s="7">
         <v>527.4299999999999</v>
@@ -2665,10 +2665,10 @@
         <v>4</v>
       </c>
       <c r="D47" s="9">
-        <v>1.67095</v>
+        <v>1.79813</v>
       </c>
       <c r="E47" s="7">
-        <v>103.78</v>
+        <v>111.68</v>
       </c>
       <c r="F47" s="7">
         <v>114.16</v>
@@ -2685,10 +2685,10 @@
         <v>4</v>
       </c>
       <c r="D48" s="9">
-        <v>1.45901</v>
+        <v>1.55546</v>
       </c>
       <c r="E48" s="7">
-        <v>72.31999999999999</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="F48" s="7">
         <v>78.59</v>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="D49" s="9"/>
       <c r="E49" s="11">
-        <v>967.24</v>
+        <v>708.22</v>
       </c>
       <c r="F49" s="11">
         <v>720.1799999999999</v>
